--- a/Result/09-01-25/NASDAQstock_09-01-25period252RS90.xlsx
+++ b/Result/09-01-25/NASDAQstock_09-01-25period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/09-01-25/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE268F4B-17E9-E14A-AB9E-9F18FB906A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -784,12 +790,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -797,17 +803,30 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -837,24 +856,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -892,7 +920,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -926,6 +954,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -960,9 +989,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1135,9 +1165,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN116"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
@@ -1262,11 +1292,11 @@
       </c>
     </row>
     <row r="2" spans="1:40">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B2">
-        <v>92.06875753920386</v>
+        <v>92.068757539203858</v>
       </c>
       <c r="C2">
         <v>290</v>
@@ -1278,31 +1308,31 @@
         <v>2.88</v>
       </c>
       <c r="F2">
-        <v>-0.0801344669370936</v>
+        <v>-8.0134466937093599E-2</v>
       </c>
       <c r="G2">
         <v>2.87</v>
       </c>
       <c r="H2">
-        <v>-0.2174500110415009</v>
+        <v>-0.21745001104150091</v>
       </c>
       <c r="I2">
-        <v>35.77599945068359</v>
+        <v>35.775999450683592</v>
       </c>
       <c r="J2">
-        <v>33.89299983978272</v>
+        <v>33.892999839782718</v>
       </c>
       <c r="K2">
-        <v>32.48619987487793</v>
+        <v>32.486199874877933</v>
       </c>
       <c r="L2">
-        <v>25.68994995117188</v>
+        <v>25.689949951171879</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -1317,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -1347,10 +1377,10 @@
         <v>111.07</v>
       </c>
       <c r="AD2">
-        <v>131.11</v>
+        <v>131.11000000000001</v>
       </c>
       <c r="AE2">
-        <v>-98.56999999999999</v>
+        <v>-98.57</v>
       </c>
       <c r="AF2">
         <v>366.67</v>
@@ -1385,7 +1415,7 @@
         <v>41</v>
       </c>
       <c r="B3">
-        <v>97.51206272617611</v>
+        <v>97.512062726176111</v>
       </c>
       <c r="C3">
         <v>669</v>
@@ -1403,16 +1433,16 @@
         <v>2.63</v>
       </c>
       <c r="H3">
-        <v>-0.2915166567868474</v>
+        <v>-0.29151665678684741</v>
       </c>
       <c r="I3">
-        <v>45.00399932861328</v>
+        <v>45.003999328613283</v>
       </c>
       <c r="J3">
-        <v>43.38549976348877</v>
+        <v>43.385499763488767</v>
       </c>
       <c r="K3">
-        <v>37.39239971160889</v>
+        <v>37.392399711608888</v>
       </c>
       <c r="L3">
         <v>25.61699993133545</v>
@@ -1436,7 +1466,7 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>9.444444444444443</v>
+        <v>9.4444444444444429</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -1460,13 +1490,13 @@
         <v>155</v>
       </c>
       <c r="AB3">
-        <v>305.15</v>
+        <v>305.14999999999998</v>
       </c>
       <c r="AC3">
         <v>808.13</v>
       </c>
       <c r="AD3">
-        <v>-9.390000000000001</v>
+        <v>-9.39</v>
       </c>
       <c r="AE3">
         <v>275</v>
@@ -1475,7 +1505,7 @@
         <v>-39.76</v>
       </c>
       <c r="AG3">
-        <v>134.95</v>
+        <v>134.94999999999999</v>
       </c>
       <c r="AH3" t="s">
         <v>158</v>
@@ -1496,7 +1526,7 @@
         <v>137.37</v>
       </c>
       <c r="AN3">
-        <v>64.6128753277326</v>
+        <v>64.612875327732596</v>
       </c>
     </row>
     <row r="4" spans="1:40">
@@ -1504,7 +1534,7 @@
         <v>42</v>
       </c>
       <c r="B4">
-        <v>97.6779252110977</v>
+        <v>97.677925211097701</v>
       </c>
       <c r="C4">
         <v>553</v>
@@ -1516,25 +1546,25 @@
         <v>1.95</v>
       </c>
       <c r="F4">
-        <v>-0.2548975427715583</v>
+        <v>-0.25489754277155829</v>
       </c>
       <c r="G4">
         <v>2.36</v>
       </c>
       <c r="H4">
-        <v>-0.3748416332503622</v>
+        <v>-0.37484163325036218</v>
       </c>
       <c r="I4">
-        <v>107.0839996337891</v>
+        <v>107.08399963378911</v>
       </c>
       <c r="J4">
         <v>110.7190002441406</v>
       </c>
       <c r="K4">
-        <v>108.0716003417969</v>
+        <v>108.07160034179689</v>
       </c>
       <c r="L4">
-        <v>82.35895009994506</v>
+        <v>82.358950099945062</v>
       </c>
       <c r="M4">
         <v>0.97</v>
@@ -1588,7 +1618,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="AF4">
         <v>450</v>
@@ -1615,15 +1645,15 @@
         <v>1306.67</v>
       </c>
       <c r="AN4">
-        <v>63.38185798720649</v>
+        <v>63.381857987206487</v>
       </c>
     </row>
     <row r="5" spans="1:40">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B5">
-        <v>96.72798552472858</v>
+        <v>96.727985524728581</v>
       </c>
       <c r="C5">
         <v>1244</v>
@@ -1635,25 +1665,25 @@
         <v>1.95</v>
       </c>
       <c r="F5">
-        <v>-0.2548975427715583</v>
+        <v>-0.25489754277155829</v>
       </c>
       <c r="G5">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="H5">
-        <v>-0.3995305151654777</v>
+        <v>-0.39953051516547772</v>
       </c>
       <c r="I5">
-        <v>467.4140014648438</v>
+        <v>467.41400146484381</v>
       </c>
       <c r="J5">
-        <v>465.1750015258789</v>
+        <v>465.17500152587888</v>
       </c>
       <c r="K5">
-        <v>452.4456005859375</v>
+        <v>452.44560058593748</v>
       </c>
       <c r="L5">
-        <v>355.1957000732422</v>
+        <v>355.19570007324222</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -1734,7 +1764,7 @@
         <v>154.57</v>
       </c>
       <c r="AN5">
-        <v>62.39216135716954</v>
+        <v>62.392161357169542</v>
       </c>
     </row>
     <row r="6" spans="1:40">
@@ -1742,7 +1772,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>99.72858866103739</v>
+        <v>99.728588661037392</v>
       </c>
       <c r="C6">
         <v>457</v>
@@ -1754,7 +1784,7 @@
         <v>4.24</v>
       </c>
       <c r="F6">
-        <v>0.1754330418100808</v>
+        <v>0.17543304181008079</v>
       </c>
       <c r="G6">
         <v>7.43</v>
@@ -1763,22 +1793,22 @@
         <v>1.189816258120082</v>
       </c>
       <c r="I6">
-        <v>341.3130004882813</v>
+        <v>341.31300048828132</v>
       </c>
       <c r="J6">
-        <v>334.9462493896484</v>
+        <v>334.94624938964841</v>
       </c>
       <c r="K6">
-        <v>302.4175988769532</v>
+        <v>302.41759887695321</v>
       </c>
       <c r="L6">
-        <v>144.5285747909546</v>
+        <v>144.52857479095459</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1820,7 +1850,7 @@
         <v>313.2</v>
       </c>
       <c r="AC6">
-        <v>312.71</v>
+        <v>312.70999999999998</v>
       </c>
       <c r="AD6">
         <v>113.12</v>
@@ -1857,11 +1887,11 @@
       </c>
     </row>
     <row r="7" spans="1:40">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B7">
-        <v>98.32629674306393</v>
+        <v>98.326296743063935</v>
       </c>
       <c r="C7">
         <v>115</v>
@@ -1870,34 +1900,34 @@
         <v>40.81</v>
       </c>
       <c r="E7">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="F7">
-        <v>0.2505999561474849</v>
+        <v>0.25059995614748493</v>
       </c>
       <c r="G7">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H7">
-        <v>0.4090303675545547</v>
+        <v>0.40903036755455469</v>
       </c>
       <c r="I7">
         <v>40.97399978637695</v>
       </c>
       <c r="J7">
-        <v>39.44000034332275</v>
+        <v>39.440000343322751</v>
       </c>
       <c r="K7">
-        <v>35.71160011291504</v>
+        <v>35.711600112915043</v>
       </c>
       <c r="L7">
-        <v>24.66202500343323</v>
+        <v>24.662025003433229</v>
       </c>
       <c r="M7">
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1948,7 +1978,7 @@
         <v>-19.05</v>
       </c>
       <c r="AF7">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AG7">
         <v>800</v>
@@ -1963,7 +1993,7 @@
         <v>208</v>
       </c>
       <c r="AK7">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AL7">
         <v>0.73</v>
@@ -1972,15 +2002,15 @@
         <v>25.86</v>
       </c>
       <c r="AN7">
-        <v>60.5369243539476</v>
+        <v>60.536924353947597</v>
       </c>
     </row>
     <row r="8" spans="1:40">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B8">
-        <v>98.80880579010856</v>
+        <v>98.808805790108565</v>
       </c>
       <c r="C8">
         <v>507</v>
@@ -1992,25 +2022,25 @@
         <v>4.51</v>
       </c>
       <c r="F8">
-        <v>0.2261707089878285</v>
+        <v>0.22617070898782851</v>
       </c>
       <c r="G8">
         <v>7.52</v>
       </c>
       <c r="H8">
-        <v>1.217591250274587</v>
+        <v>1.2175912502745869</v>
       </c>
       <c r="I8">
-        <v>73.65199890136719</v>
+        <v>73.651998901367193</v>
       </c>
       <c r="J8">
-        <v>70.78499946594238</v>
+        <v>70.784999465942377</v>
       </c>
       <c r="K8">
-        <v>57.29499977111816</v>
+        <v>57.294999771118157</v>
       </c>
       <c r="L8">
-        <v>34.67877495765686</v>
+        <v>34.678774957656863</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2067,10 +2097,10 @@
         <v>50</v>
       </c>
       <c r="AF8">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="AG8">
-        <v>-2422.22</v>
+        <v>-2422.2199999999998</v>
       </c>
       <c r="AH8" t="s">
         <v>162</v>
@@ -2082,7 +2112,7 @@
         <v>209</v>
       </c>
       <c r="AK8">
-        <v>-0.14</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="AL8">
         <v>0.77</v>
@@ -2091,7 +2121,7 @@
         <v>650</v>
       </c>
       <c r="AN8">
-        <v>59.7431087157097</v>
+        <v>59.743108715709702</v>
       </c>
     </row>
     <row r="9" spans="1:40">
@@ -2099,13 +2129,13 @@
         <v>47</v>
       </c>
       <c r="B9">
-        <v>91.64656212303981</v>
+        <v>91.646562123039814</v>
       </c>
       <c r="C9">
         <v>566</v>
       </c>
       <c r="D9">
-        <v>32.55</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="E9">
         <v>1.99</v>
@@ -2117,7 +2147,7 @@
         <v>1.96</v>
       </c>
       <c r="H9">
-        <v>-0.4982860428259396</v>
+        <v>-0.49828604282593958</v>
       </c>
       <c r="I9">
         <v>31.46599998474121</v>
@@ -2126,7 +2156,7 @@
         <v>30.07049989700317</v>
       </c>
       <c r="K9">
-        <v>29.43711608886719</v>
+        <v>29.437116088867189</v>
       </c>
       <c r="L9">
         <v>26.92300729751587</v>
@@ -2150,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -2162,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>18.19</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="Y9">
         <v>32.64</v>
@@ -2186,7 +2216,7 @@
         <v>48.84</v>
       </c>
       <c r="AF9">
-        <v>19.44</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="AG9">
         <v>200</v>
@@ -2210,7 +2240,7 @@
         <v>30.46</v>
       </c>
       <c r="AN9">
-        <v>59.20896165211684</v>
+        <v>59.208961652116841</v>
       </c>
     </row>
     <row r="10" spans="1:40">
@@ -2218,7 +2248,7 @@
         <v>48</v>
       </c>
       <c r="B10">
-        <v>96.12484921592281</v>
+        <v>96.124849215922808</v>
       </c>
       <c r="C10">
         <v>636</v>
@@ -2227,28 +2257,28 @@
         <v>30.53</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F10">
-        <v>-0.2398641599040776</v>
+        <v>-0.23986415990407761</v>
       </c>
       <c r="G10">
         <v>3.14</v>
       </c>
       <c r="H10">
-        <v>-0.1341250345779861</v>
+        <v>-0.13412503457798611</v>
       </c>
       <c r="I10">
-        <v>29.69400024414062</v>
+        <v>29.694000244140621</v>
       </c>
       <c r="J10">
-        <v>28.25349998474121</v>
+        <v>28.253499984741211</v>
       </c>
       <c r="K10">
-        <v>24.27839996337891</v>
+        <v>24.278399963378909</v>
       </c>
       <c r="L10">
-        <v>16.83545001506806</v>
+        <v>16.835450015068059</v>
       </c>
       <c r="M10">
         <v>1.05</v>
@@ -2320,7 +2350,7 @@
         <v>211</v>
       </c>
       <c r="AK10">
-        <v>-0.07000000000000001</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="AL10">
         <v>0.7</v>
@@ -2329,7 +2359,7 @@
         <v>1100</v>
       </c>
       <c r="AN10">
-        <v>56.85790761513814</v>
+        <v>56.857907615138139</v>
       </c>
     </row>
     <row r="11" spans="1:40">
@@ -2337,7 +2367,7 @@
         <v>49</v>
       </c>
       <c r="B11">
-        <v>99.06513872135102</v>
+        <v>99.065138721351019</v>
       </c>
       <c r="C11">
         <v>1467</v>
@@ -2346,28 +2376,28 @@
         <v>71</v>
       </c>
       <c r="E11">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="F11">
-        <v>0.1510037946504244</v>
+        <v>0.15100379465042441</v>
       </c>
       <c r="G11">
         <v>3.07</v>
       </c>
       <c r="H11">
-        <v>-0.1557278062537122</v>
+        <v>-0.15572780625371219</v>
       </c>
       <c r="I11">
-        <v>70.65000152587891</v>
+        <v>70.650001525878906</v>
       </c>
       <c r="J11">
-        <v>65.18550109863281</v>
+        <v>65.185501098632812</v>
       </c>
       <c r="K11">
-        <v>59.37700019836426</v>
+        <v>59.377000198364257</v>
       </c>
       <c r="L11">
-        <v>40.2633950805664</v>
+        <v>40.263395080566397</v>
       </c>
       <c r="M11">
         <v>1.08</v>
@@ -2448,11 +2478,11 @@
         <v>36.92</v>
       </c>
       <c r="AN11">
-        <v>53.7114785415494</v>
+        <v>53.711478541549397</v>
       </c>
     </row>
     <row r="12" spans="1:40">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B12">
@@ -2468,7 +2498,7 @@
         <v>2.93</v>
       </c>
       <c r="F12">
-        <v>-0.07073860264491802</v>
+        <v>-7.0738602644918019E-2</v>
       </c>
       <c r="G12">
         <v>2.89</v>
@@ -2477,16 +2507,16 @@
         <v>-0.211277790562722</v>
       </c>
       <c r="I12">
-        <v>359.8580017089844</v>
+        <v>359.85800170898438</v>
       </c>
       <c r="J12">
-        <v>340.8654998779297</v>
+        <v>340.86549987792972</v>
       </c>
       <c r="K12">
-        <v>333.2705627441406</v>
+        <v>333.27056274414059</v>
       </c>
       <c r="L12">
-        <v>246.6259707729494</v>
+        <v>246.62597077294939</v>
       </c>
       <c r="M12">
         <v>1.06</v>
@@ -2561,7 +2591,7 @@
         <v>63.9</v>
       </c>
       <c r="AN12">
-        <v>53.24326537279713</v>
+        <v>53.243265372797133</v>
       </c>
     </row>
     <row r="13" spans="1:40">
@@ -2569,7 +2599,7 @@
         <v>51</v>
       </c>
       <c r="B13">
-        <v>92.27985524728589</v>
+        <v>92.279855247285894</v>
       </c>
       <c r="C13">
         <v>843</v>
@@ -2581,13 +2611,13 @@
         <v>2.14</v>
       </c>
       <c r="F13">
-        <v>-0.2191932584612913</v>
+        <v>-0.21919325846129131</v>
       </c>
       <c r="G13">
         <v>1.75</v>
       </c>
       <c r="H13">
-        <v>-0.5630943578531177</v>
+        <v>-0.56309435785311768</v>
       </c>
       <c r="I13">
         <v>172.8700012207031</v>
@@ -2596,7 +2626,7 @@
         <v>172.2660003662109</v>
       </c>
       <c r="K13">
-        <v>171.3631994628906</v>
+        <v>171.36319946289061</v>
       </c>
       <c r="L13">
         <v>136.4178494262695</v>
@@ -2650,16 +2680,16 @@
         <v>303.93</v>
       </c>
       <c r="AD13">
-        <v>-2.43</v>
+        <v>-2.4300000000000002</v>
       </c>
       <c r="AE13">
         <v>202.63</v>
       </c>
       <c r="AF13">
-        <v>-533.33</v>
+        <v>-533.33000000000004</v>
       </c>
       <c r="AG13">
-        <v>84.20999999999999</v>
+        <v>84.21</v>
       </c>
       <c r="AH13" t="s">
         <v>164</v>
@@ -2677,10 +2707,10 @@
         <v>1.78</v>
       </c>
       <c r="AM13">
-        <v>513.95</v>
+        <v>513.95000000000005</v>
       </c>
       <c r="AN13">
-        <v>51.42120068768376</v>
+        <v>51.421200687683758</v>
       </c>
     </row>
     <row r="14" spans="1:40">
@@ -2700,25 +2730,25 @@
         <v>3.83</v>
       </c>
       <c r="F14">
-        <v>0.09838695461424142</v>
+        <v>9.838695461424142E-2</v>
       </c>
       <c r="G14">
         <v>3.75</v>
       </c>
       <c r="H14">
-        <v>0.05412769002476944</v>
+        <v>5.4127690024769443E-2</v>
       </c>
       <c r="I14">
         <v>14.74400005340576</v>
       </c>
       <c r="J14">
-        <v>15.57599992752075</v>
+        <v>15.575999927520749</v>
       </c>
       <c r="K14">
         <v>14.536399974823</v>
       </c>
       <c r="L14">
-        <v>9.218524987697601</v>
+        <v>9.2185249876976005</v>
       </c>
       <c r="M14">
         <v>0.95</v>
@@ -2739,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="T14">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -2754,7 +2784,7 @@
         <v>6.01</v>
       </c>
       <c r="Y14">
-        <v>17.19</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="Z14">
         <v>15.79</v>
@@ -2793,13 +2823,13 @@
         <v>0.12</v>
       </c>
       <c r="AL14">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AM14">
-        <v>141.67</v>
+        <v>141.66999999999999</v>
       </c>
       <c r="AN14">
-        <v>51.33675140848274</v>
+        <v>51.336751408482741</v>
       </c>
     </row>
     <row r="15" spans="1:40">
@@ -2819,25 +2849,25 @@
         <v>2.14</v>
       </c>
       <c r="F15">
-        <v>-0.2191932584612913</v>
+        <v>-0.21919325846129131</v>
       </c>
       <c r="G15">
         <v>2.13</v>
       </c>
       <c r="H15">
-        <v>-0.4458221687563192</v>
+        <v>-0.44582216875631919</v>
       </c>
       <c r="I15">
-        <v>145.5580047607422</v>
+        <v>145.55800476074219</v>
       </c>
       <c r="J15">
-        <v>138.6065010070801</v>
+        <v>138.60650100708011</v>
       </c>
       <c r="K15">
         <v>138.3002008056641</v>
       </c>
       <c r="L15">
-        <v>115.1495500946045</v>
+        <v>115.14955009460451</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -2858,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -2873,7 +2903,7 @@
         <v>60.96</v>
       </c>
       <c r="Y15">
-        <v>150.55</v>
+        <v>150.55000000000001</v>
       </c>
       <c r="Z15">
         <v>11.61</v>
@@ -2909,7 +2939,7 @@
         <v>215</v>
       </c>
       <c r="AK15">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AL15">
         <v>5.42</v>
@@ -2918,7 +2948,7 @@
         <v>379.65</v>
       </c>
       <c r="AN15">
-        <v>49.05956306608206</v>
+        <v>49.059563066082063</v>
       </c>
     </row>
     <row r="16" spans="1:40">
@@ -2926,7 +2956,7 @@
         <v>54</v>
       </c>
       <c r="B16">
-        <v>93.77261761158022</v>
+        <v>93.772617611580216</v>
       </c>
       <c r="C16">
         <v>564</v>
@@ -2944,19 +2974,19 @@
         <v>2.59</v>
       </c>
       <c r="H16">
-        <v>-0.3038610977444052</v>
+        <v>-0.30386109774440517</v>
       </c>
       <c r="I16">
-        <v>43.95600051879883</v>
+        <v>43.956000518798831</v>
       </c>
       <c r="J16">
-        <v>42.71600036621093</v>
+        <v>42.716000366210928</v>
       </c>
       <c r="K16">
-        <v>43.69310020446778</v>
+        <v>43.693100204467783</v>
       </c>
       <c r="L16">
-        <v>37.78600005149841</v>
+        <v>37.786000051498412</v>
       </c>
       <c r="M16">
         <v>1.03</v>
@@ -3037,7 +3067,7 @@
         <v>-87.3</v>
       </c>
       <c r="AN16">
-        <v>48.09568202789612</v>
+        <v>48.095682027896117</v>
       </c>
     </row>
     <row r="17" spans="1:40">
@@ -3045,7 +3075,7 @@
         <v>55</v>
       </c>
       <c r="B17">
-        <v>92.3854041013269</v>
+        <v>92.385404101326898</v>
       </c>
       <c r="C17">
         <v>2031</v>
@@ -3057,19 +3087,19 @@
         <v>1.43</v>
       </c>
       <c r="F17">
-        <v>-0.3526145314101838</v>
+        <v>-0.35261453141018378</v>
       </c>
       <c r="G17">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="H17">
-        <v>-0.4766832711502136</v>
+        <v>-0.47668327115021358</v>
       </c>
       <c r="I17">
         <v>142.1819976806641</v>
       </c>
       <c r="J17">
-        <v>143.1604988098144</v>
+        <v>143.16049880981441</v>
       </c>
       <c r="K17">
         <v>133.6631993103027</v>
@@ -3108,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>75.34999999999999</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="Y17">
         <v>149.4</v>
@@ -3135,7 +3165,7 @@
         <v>157.94</v>
       </c>
       <c r="AG17">
-        <v>-641.1799999999999</v>
+        <v>-641.17999999999995</v>
       </c>
       <c r="AH17" t="s">
         <v>162</v>
@@ -3156,7 +3186,7 @@
         <v>836.36</v>
       </c>
       <c r="AN17">
-        <v>46.47795004067084</v>
+        <v>46.477950040670841</v>
       </c>
     </row>
     <row r="18" spans="1:40">
@@ -3164,7 +3194,7 @@
         <v>56</v>
       </c>
       <c r="B18">
-        <v>92.61158021712907</v>
+        <v>92.611580217129074</v>
       </c>
       <c r="C18">
         <v>737</v>
@@ -3176,25 +3206,25 @@
         <v>1.3</v>
       </c>
       <c r="F18">
-        <v>-0.3770437785698401</v>
+        <v>-0.37704377856984012</v>
       </c>
       <c r="G18">
         <v>1.99</v>
       </c>
       <c r="H18">
-        <v>-0.4890277121077712</v>
+        <v>-0.48902771210777118</v>
       </c>
       <c r="I18">
-        <v>880.7519897460937</v>
+        <v>880.75198974609373</v>
       </c>
       <c r="J18">
-        <v>905.297494506836</v>
+        <v>905.29749450683596</v>
       </c>
       <c r="K18">
         <v>865.3063952636719</v>
       </c>
       <c r="L18">
-        <v>708.5327987670898</v>
+        <v>708.53279876708984</v>
       </c>
       <c r="M18">
         <v>0.97</v>
@@ -3215,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -3275,7 +3305,7 @@
         <v>34.5</v>
       </c>
       <c r="AN18">
-        <v>44.38985255718529</v>
+        <v>44.389852557185293</v>
       </c>
     </row>
     <row r="19" spans="1:40">
@@ -3283,7 +3313,7 @@
         <v>57</v>
       </c>
       <c r="B19">
-        <v>94.72255729794934</v>
+        <v>94.722557297949336</v>
       </c>
       <c r="C19">
         <v>990</v>
@@ -3295,25 +3325,25 @@
         <v>1.79</v>
       </c>
       <c r="F19">
-        <v>-0.28496430850652</v>
+        <v>-0.28496430850651999</v>
       </c>
       <c r="G19">
         <v>2.02</v>
       </c>
       <c r="H19">
-        <v>-0.479769381389603</v>
+        <v>-0.47976938138960301</v>
       </c>
       <c r="I19">
-        <v>80.20799865722657</v>
+        <v>80.207998657226568</v>
       </c>
       <c r="J19">
-        <v>79.09700012207031</v>
+        <v>79.097000122070312</v>
       </c>
       <c r="K19">
-        <v>75.55686889648437</v>
+        <v>75.556868896484374</v>
       </c>
       <c r="L19">
-        <v>57.81150003433228</v>
+        <v>57.811500034332283</v>
       </c>
       <c r="M19">
         <v>1.01</v>
@@ -3349,7 +3379,7 @@
         <v>37.83</v>
       </c>
       <c r="Y19">
-        <v>82.68000000000001</v>
+        <v>82.68</v>
       </c>
       <c r="Z19">
         <v>16.47</v>
@@ -3373,7 +3403,7 @@
         <v>-2.94</v>
       </c>
       <c r="AG19">
-        <v>134.48</v>
+        <v>134.47999999999999</v>
       </c>
       <c r="AH19" t="s">
         <v>168</v>
@@ -3394,11 +3424,11 @@
         <v>51.01</v>
       </c>
       <c r="AN19">
-        <v>43.0151163178945</v>
+        <v>43.015116317894503</v>
       </c>
     </row>
     <row r="20" spans="1:40">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B20">
@@ -3420,13 +3450,13 @@
         <v>1.91</v>
       </c>
       <c r="H20">
-        <v>-0.5137165940228867</v>
+        <v>-0.51371659402288672</v>
       </c>
       <c r="I20">
         <v>187.0380004882812</v>
       </c>
       <c r="J20">
-        <v>181.6744987487793</v>
+        <v>181.67449874877931</v>
       </c>
       <c r="K20">
         <v>186.782571105957</v>
@@ -3453,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -3465,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>79.23999999999999</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="Y20">
         <v>209.87</v>
@@ -3513,15 +3543,15 @@
         <v>49.37</v>
       </c>
       <c r="AN20">
-        <v>42.33455206940076</v>
+        <v>42.334552069400758</v>
       </c>
     </row>
     <row r="21" spans="1:40">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B21">
-        <v>97.52714113389625</v>
+        <v>97.527141133896251</v>
       </c>
       <c r="C21">
         <v>1489</v>
@@ -3539,10 +3569,10 @@
         <v>3.51</v>
       </c>
       <c r="H21">
-        <v>-0.01993895572057709</v>
+        <v>-1.9938955720577089E-2</v>
       </c>
       <c r="I21">
-        <v>169.4940002441406</v>
+        <v>169.49400024414061</v>
       </c>
       <c r="J21">
         <v>164.4675003051758</v>
@@ -3557,7 +3587,7 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -3599,7 +3629,7 @@
         <v>57.13</v>
       </c>
       <c r="AC21">
-        <v>73.04000000000001</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="AD21">
         <v>-25.82</v>
@@ -3632,7 +3662,7 @@
         <v>31.64</v>
       </c>
       <c r="AN21">
-        <v>40.90825715651852</v>
+        <v>40.908257156518523</v>
       </c>
     </row>
     <row r="22" spans="1:40">
@@ -3640,7 +3670,7 @@
         <v>60</v>
       </c>
       <c r="B22">
-        <v>98.94451145958986</v>
+        <v>98.944511459589862</v>
       </c>
       <c r="C22">
         <v>17</v>
@@ -3658,25 +3688,25 @@
         <v>4.71</v>
       </c>
       <c r="H22">
-        <v>0.3503942730061553</v>
+        <v>0.35039427300615528</v>
       </c>
       <c r="I22">
-        <v>73.84400024414063</v>
+        <v>73.844000244140631</v>
       </c>
       <c r="J22">
         <v>75.77000007629394</v>
       </c>
       <c r="K22">
-        <v>66.08019989013673</v>
+        <v>66.080199890136726</v>
       </c>
       <c r="L22">
-        <v>37.8837999534607</v>
+        <v>37.883799953460702</v>
       </c>
       <c r="M22">
         <v>0.97</v>
       </c>
       <c r="N22">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3751,33 +3781,33 @@
         <v>135</v>
       </c>
       <c r="AN22">
-        <v>40.47952333532287</v>
+        <v>40.479523335322867</v>
       </c>
     </row>
     <row r="23" spans="1:40">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B23">
-        <v>97.31604342581423</v>
+        <v>97.316043425814229</v>
       </c>
       <c r="C23">
         <v>336</v>
       </c>
       <c r="D23">
-        <v>129.27</v>
+        <v>129.27000000000001</v>
       </c>
       <c r="E23">
         <v>3.38</v>
       </c>
       <c r="F23">
-        <v>0.01382417598466166</v>
+        <v>1.3824175984661661E-2</v>
       </c>
       <c r="G23">
         <v>3.51</v>
       </c>
       <c r="H23">
-        <v>-0.01993895572057709</v>
+        <v>-1.9938955720577089E-2</v>
       </c>
       <c r="I23">
         <v>127.5920013427734</v>
@@ -3831,7 +3861,7 @@
         <v>48.52</v>
       </c>
       <c r="AA23">
-        <v>82.84999999999999</v>
+        <v>82.85</v>
       </c>
       <c r="AB23">
         <v>51.1</v>
@@ -3867,18 +3897,18 @@
         <v>3.44</v>
       </c>
       <c r="AM23">
-        <v>129.33</v>
+        <v>129.33000000000001</v>
       </c>
       <c r="AN23">
-        <v>40.22553141896774</v>
+        <v>40.225531418967741</v>
       </c>
     </row>
     <row r="24" spans="1:40">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B24">
-        <v>93.25995174909529</v>
+        <v>93.259951749095293</v>
       </c>
       <c r="C24">
         <v>2326</v>
@@ -3890,7 +3920,7 @@
         <v>1.96</v>
       </c>
       <c r="F24">
-        <v>-0.2530183699131233</v>
+        <v>-0.25301836991312332</v>
       </c>
       <c r="G24">
         <v>2.86</v>
@@ -3902,10 +3932,10 @@
         <v>222.2860015869141</v>
       </c>
       <c r="J24">
-        <v>219.7474998474121</v>
+        <v>219.74749984741209</v>
       </c>
       <c r="K24">
-        <v>204.2841003417969</v>
+        <v>204.28410034179689</v>
       </c>
       <c r="L24">
         <v>166.1803503417969</v>
@@ -3914,7 +3944,7 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -3989,15 +4019,15 @@
         <v>338.36</v>
       </c>
       <c r="AN24">
-        <v>39.43756091200206</v>
+        <v>39.437560912002063</v>
       </c>
     </row>
     <row r="25" spans="1:40">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B25">
-        <v>98.5524728588661</v>
+        <v>98.552472858866096</v>
       </c>
       <c r="C25">
         <v>1050</v>
@@ -4009,31 +4039,31 @@
         <v>3.15</v>
       </c>
       <c r="F25">
-        <v>-0.02939679975934576</v>
+        <v>-2.9396799759345761E-2</v>
       </c>
       <c r="G25">
         <v>3.74</v>
       </c>
       <c r="H25">
-        <v>0.05104157978538007</v>
+        <v>5.104157978538007E-2</v>
       </c>
       <c r="I25">
-        <v>97.8979995727539</v>
+        <v>97.897999572753903</v>
       </c>
       <c r="J25">
-        <v>95.48099975585937</v>
+        <v>95.480999755859372</v>
       </c>
       <c r="K25">
-        <v>87.84240005493164</v>
+        <v>87.842400054931645</v>
       </c>
       <c r="L25">
-        <v>60.82270002365112</v>
+        <v>60.822700023651123</v>
       </c>
       <c r="M25">
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -4112,11 +4142,11 @@
       </c>
     </row>
     <row r="26" spans="1:40">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B26">
-        <v>97.49698431845597</v>
+        <v>97.496984318455972</v>
       </c>
       <c r="C26">
         <v>4621</v>
@@ -4125,28 +4155,28 @@
         <v>357.02</v>
       </c>
       <c r="E26">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F26">
-        <v>-0.2116765670275509</v>
+        <v>-0.21167656702755089</v>
       </c>
       <c r="G26">
         <v>3.45</v>
       </c>
       <c r="H26">
-        <v>-0.03845561715691358</v>
+        <v>-3.8455617156913577E-2</v>
       </c>
       <c r="I26">
-        <v>349.7220031738281</v>
+        <v>349.72200317382811</v>
       </c>
       <c r="J26">
-        <v>343.3855026245117</v>
+        <v>343.38550262451167</v>
       </c>
       <c r="K26">
-        <v>328.8714428710937</v>
+        <v>328.87144287109368</v>
       </c>
       <c r="L26">
-        <v>205.6115432357788</v>
+        <v>205.61154323577881</v>
       </c>
       <c r="M26">
         <v>1.02</v>
@@ -4197,7 +4227,7 @@
         <v>45.75</v>
       </c>
       <c r="AD26">
-        <v>623.9400000000001</v>
+        <v>623.94000000000005</v>
       </c>
       <c r="AE26">
         <v>23.26</v>
@@ -4221,13 +4251,13 @@
         <v>6.46</v>
       </c>
       <c r="AL26">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="AM26">
         <v>57.89</v>
       </c>
       <c r="AN26">
-        <v>38.87571651764176</v>
+        <v>38.875716517641763</v>
       </c>
     </row>
     <row r="27" spans="1:40">
@@ -4235,7 +4265,7 @@
         <v>65</v>
       </c>
       <c r="B27">
-        <v>91.39022919179735</v>
+        <v>91.390229191797346</v>
       </c>
       <c r="C27">
         <v>187</v>
@@ -4247,25 +4277,25 @@
         <v>1.87</v>
       </c>
       <c r="F27">
-        <v>-0.2699309256390391</v>
+        <v>-0.26993092563903909</v>
       </c>
       <c r="G27">
         <v>1.76</v>
       </c>
       <c r="H27">
-        <v>-0.5600082476137282</v>
+        <v>-0.56000824761372825</v>
       </c>
       <c r="I27">
         <v>612.5359985351563</v>
       </c>
       <c r="J27">
-        <v>608.6501190185547</v>
+        <v>608.65011901855473</v>
       </c>
       <c r="K27">
         <v>591.4863256835938</v>
       </c>
       <c r="L27">
-        <v>530.003875579834</v>
+        <v>530.00387557983402</v>
       </c>
       <c r="M27">
         <v>1.01</v>
@@ -4316,10 +4346,10 @@
         <v>37.58</v>
       </c>
       <c r="AD27">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="AE27">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="AF27">
         <v>9.26</v>
@@ -4343,18 +4373,18 @@
         <v>25.3</v>
       </c>
       <c r="AM27">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="AN27">
-        <v>38.80413024460585</v>
+        <v>38.804130244605851</v>
       </c>
     </row>
     <row r="28" spans="1:40">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B28">
-        <v>95.46139927623642</v>
+        <v>95.461399276236421</v>
       </c>
       <c r="C28">
         <v>886</v>
@@ -4366,25 +4396,25 @@
         <v>1.57</v>
       </c>
       <c r="F28">
-        <v>-0.3263061113920923</v>
+        <v>-0.32630611139209231</v>
       </c>
       <c r="G28">
         <v>2.27</v>
       </c>
       <c r="H28">
-        <v>-0.402616625404867</v>
+        <v>-0.40261662540486698</v>
       </c>
       <c r="I28">
-        <v>112.5460021972656</v>
+        <v>112.54600219726559</v>
       </c>
       <c r="J28">
-        <v>111.9545009613037</v>
+        <v>111.95450096130369</v>
       </c>
       <c r="K28">
         <v>112.2516000366211</v>
       </c>
       <c r="L28">
-        <v>91.86930913925171</v>
+        <v>91.869309139251712</v>
       </c>
       <c r="M28">
         <v>1.01</v>
@@ -4465,15 +4495,15 @@
         <v>21.92</v>
       </c>
       <c r="AN28">
-        <v>38.78287449537064</v>
+        <v>38.782874495370642</v>
       </c>
     </row>
     <row r="29" spans="1:40">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B29">
-        <v>98.95958986731002</v>
+        <v>98.959589867310015</v>
       </c>
       <c r="C29">
         <v>321</v>
@@ -4485,31 +4515,31 @@
         <v>3.6</v>
       </c>
       <c r="F29">
-        <v>0.055165978870234</v>
+        <v>5.5165978870234E-2</v>
       </c>
       <c r="G29">
         <v>3.81</v>
       </c>
       <c r="H29">
-        <v>0.07264435146110607</v>
+        <v>7.2644351461106066E-2</v>
       </c>
       <c r="I29">
         <v>160.0299987792969</v>
       </c>
       <c r="J29">
-        <v>145.8423599243164</v>
+        <v>145.84235992431641</v>
       </c>
       <c r="K29">
-        <v>144.7894300842285</v>
+        <v>144.78943008422851</v>
       </c>
       <c r="L29">
         <v>102.9970523071289</v>
       </c>
       <c r="M29">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N29">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -4536,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="Y29">
         <v>168.4</v>
@@ -4548,13 +4578,13 @@
         <v>155</v>
       </c>
       <c r="AB29">
-        <v>32.27</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="AC29">
         <v>320.5</v>
       </c>
       <c r="AD29">
-        <v>37.16</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="AE29">
         <v>482.61</v>
@@ -4584,7 +4614,7 @@
         <v>29.94</v>
       </c>
       <c r="AN29">
-        <v>38.29047864078968</v>
+        <v>38.290478640789679</v>
       </c>
     </row>
     <row r="30" spans="1:40">
@@ -4592,7 +4622,7 @@
         <v>68</v>
       </c>
       <c r="B30">
-        <v>95.00904704463208</v>
+        <v>95.009047044632084</v>
       </c>
       <c r="C30">
         <v>151</v>
@@ -4604,22 +4634,22 @@
         <v>2.79</v>
       </c>
       <c r="F30">
-        <v>-0.09704702266300952</v>
+        <v>-9.7047022663009519E-2</v>
       </c>
       <c r="G30">
         <v>2.62</v>
       </c>
       <c r="H30">
-        <v>-0.2946027670262368</v>
+        <v>-0.29460276702623678</v>
       </c>
       <c r="I30">
-        <v>209.747998046875</v>
+        <v>209.74799804687501</v>
       </c>
       <c r="J30">
         <v>201.6528221130371</v>
       </c>
       <c r="K30">
-        <v>195.9266995239258</v>
+        <v>195.92669952392581</v>
       </c>
       <c r="L30">
         <v>171.284714012146</v>
@@ -4703,7 +4733,7 @@
         <v>30.53</v>
       </c>
       <c r="AN30">
-        <v>35.662082924191</v>
+        <v>35.662082924190997</v>
       </c>
     </row>
     <row r="31" spans="1:40">
@@ -4711,37 +4741,37 @@
         <v>69</v>
       </c>
       <c r="B31">
-        <v>94.48130277442702</v>
+        <v>94.481302774427022</v>
       </c>
       <c r="C31">
         <v>408</v>
       </c>
       <c r="D31">
-        <v>145.2</v>
+        <v>145.19999999999999</v>
       </c>
       <c r="E31">
         <v>3.81</v>
       </c>
       <c r="F31">
-        <v>0.09462860889737121</v>
+        <v>9.4628608897371208E-2</v>
       </c>
       <c r="G31">
         <v>3.47</v>
       </c>
       <c r="H31">
-        <v>-0.0322833966781347</v>
+        <v>-3.22833966781347E-2</v>
       </c>
       <c r="I31">
         <v>141.2540008544922</v>
       </c>
       <c r="J31">
-        <v>137.1030002593994</v>
+        <v>137.10300025939941</v>
       </c>
       <c r="K31">
-        <v>138.7716990661621</v>
+        <v>138.77169906616211</v>
       </c>
       <c r="L31">
-        <v>135.8648247146606</v>
+        <v>135.86482471466061</v>
       </c>
       <c r="M31">
         <v>1.03</v>
@@ -4780,7 +4810,7 @@
         <v>188.75</v>
       </c>
       <c r="Z31">
-        <v>152.61</v>
+        <v>152.61000000000001</v>
       </c>
       <c r="AA31" t="s">
         <v>155</v>
@@ -4798,7 +4828,7 @@
         <v>-52.38</v>
       </c>
       <c r="AF31">
-        <v>-8.699999999999999</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="AG31">
         <v>187.5</v>
@@ -4830,13 +4860,13 @@
         <v>70</v>
       </c>
       <c r="B32">
-        <v>97.66284680337756</v>
+        <v>97.662846803377562</v>
       </c>
       <c r="C32">
         <v>1233</v>
       </c>
       <c r="D32">
-        <v>140.2</v>
+        <v>140.19999999999999</v>
       </c>
       <c r="E32">
         <v>2.21</v>
@@ -4848,16 +4878,16 @@
         <v>2.1</v>
       </c>
       <c r="H32">
-        <v>-0.4550804994744874</v>
+        <v>-0.45508049947448742</v>
       </c>
       <c r="I32">
-        <v>137.5019989013672</v>
+        <v>137.50199890136719</v>
       </c>
       <c r="J32">
-        <v>136.898498916626</v>
+        <v>136.89849891662601</v>
       </c>
       <c r="K32">
-        <v>140.0627990722656</v>
+        <v>140.06279907226559</v>
       </c>
       <c r="L32">
         <v>100.7208998680115</v>
@@ -4896,7 +4926,7 @@
         <v>48.73</v>
       </c>
       <c r="Y32">
-        <v>155.64</v>
+        <v>155.63999999999999</v>
       </c>
       <c r="Z32">
         <v>14.02</v>
@@ -4941,7 +4971,7 @@
         <v>21.39</v>
       </c>
       <c r="AN32">
-        <v>33.76656197081147</v>
+        <v>33.766561970811473</v>
       </c>
     </row>
     <row r="33" spans="1:40">
@@ -4949,7 +4979,7 @@
         <v>71</v>
       </c>
       <c r="B33">
-        <v>92.21954161640531</v>
+        <v>92.219541616405309</v>
       </c>
       <c r="C33">
         <v>177</v>
@@ -4958,28 +4988,28 @@
         <v>91.8</v>
       </c>
       <c r="E33">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F33">
-        <v>-0.4071105443048018</v>
+        <v>-0.40711054430480181</v>
       </c>
       <c r="G33">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H33">
-        <v>-0.7667776336528204</v>
+        <v>-0.76677763365282037</v>
       </c>
       <c r="I33">
-        <v>90.96399993896485</v>
+        <v>90.963999938964847</v>
       </c>
       <c r="J33">
-        <v>92.49615287780762</v>
+        <v>92.496152877807617</v>
       </c>
       <c r="K33">
-        <v>89.26186737060547</v>
+        <v>89.261867370605472</v>
       </c>
       <c r="L33">
-        <v>74.31739101409912</v>
+        <v>74.317391014099115</v>
       </c>
       <c r="M33">
         <v>0.98</v>
@@ -5000,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>6.11111111111111</v>
+        <v>6.1111111111111098</v>
       </c>
       <c r="U33" t="b">
         <v>1</v>
@@ -5027,7 +5057,7 @@
         <v>11.91</v>
       </c>
       <c r="AC33">
-        <v>913.0599999999999</v>
+        <v>913.06</v>
       </c>
       <c r="AD33">
         <v>23.48</v>
@@ -5060,7 +5090,7 @@
         <v>12.4</v>
       </c>
       <c r="AN33">
-        <v>32.80795422486659</v>
+        <v>32.807954224866592</v>
       </c>
     </row>
     <row r="34" spans="1:40">
@@ -5068,7 +5098,7 @@
         <v>72</v>
       </c>
       <c r="B34">
-        <v>92.02352231604343</v>
+        <v>92.023522316043426</v>
       </c>
       <c r="C34">
         <v>2124</v>
@@ -5077,10 +5107,10 @@
         <v>211.39</v>
       </c>
       <c r="E34">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="F34">
-        <v>-0.4165064085969774</v>
+        <v>-0.41650640859697741</v>
       </c>
       <c r="G34">
         <v>3.2</v>
@@ -5089,10 +5119,10 @@
         <v>-0.1156083731416495</v>
       </c>
       <c r="I34">
-        <v>207.8940002441406</v>
+        <v>207.89400024414061</v>
       </c>
       <c r="J34">
-        <v>210.4381050109863</v>
+        <v>210.43810501098631</v>
       </c>
       <c r="K34">
         <v>208.1440368652344</v>
@@ -5137,7 +5167,7 @@
         <v>222.2</v>
       </c>
       <c r="Z34">
-        <v>40.59</v>
+        <v>40.590000000000003</v>
       </c>
       <c r="AA34">
         <v>12.9</v>
@@ -5152,10 +5182,10 @@
         <v>21.91</v>
       </c>
       <c r="AE34">
-        <v>32.48</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="AF34">
-        <v>9.029999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="AG34">
         <v>-49.12</v>
@@ -5179,7 +5209,7 @@
         <v>-5.09</v>
       </c>
       <c r="AN34">
-        <v>32.64186781955772</v>
+        <v>32.641867819557717</v>
       </c>
     </row>
     <row r="35" spans="1:40">
@@ -5187,37 +5217,37 @@
         <v>73</v>
       </c>
       <c r="B35">
-        <v>91.52593486127864</v>
+        <v>91.525934861278643</v>
       </c>
       <c r="C35">
         <v>802</v>
       </c>
       <c r="D35">
-        <v>65.79000000000001</v>
+        <v>65.790000000000006</v>
       </c>
       <c r="E35">
         <v>1.84</v>
       </c>
       <c r="F35">
-        <v>-0.2755684442143445</v>
+        <v>-0.27556844421434451</v>
       </c>
       <c r="G35">
         <v>2.97</v>
       </c>
       <c r="H35">
-        <v>-0.1865889086476065</v>
+        <v>-0.18658890864760649</v>
       </c>
       <c r="I35">
-        <v>66.41399993896485</v>
+        <v>66.413999938964849</v>
       </c>
       <c r="J35">
-        <v>66.3984998703003</v>
+        <v>66.398499870300299</v>
       </c>
       <c r="K35">
-        <v>64.71152938842773</v>
+        <v>64.711529388427735</v>
       </c>
       <c r="L35">
-        <v>50.93786823272705</v>
+        <v>50.937868232727048</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -5250,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>34.52</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="Y35">
         <v>69.39</v>
@@ -5298,15 +5328,15 @@
         <v>-15.97</v>
       </c>
       <c r="AN35">
-        <v>32.23227479831179</v>
+        <v>32.232274798311792</v>
       </c>
     </row>
     <row r="36" spans="1:40">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B36">
-        <v>93.4258142340169</v>
+        <v>93.425814234016897</v>
       </c>
       <c r="C36">
         <v>352</v>
@@ -5315,34 +5345,34 @@
         <v>115.51</v>
       </c>
       <c r="E36">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="F36">
-        <v>-0.1459055169823223</v>
+        <v>-0.14590551698232229</v>
       </c>
       <c r="G36">
         <v>2.44</v>
       </c>
       <c r="H36">
-        <v>-0.3501527513352466</v>
+        <v>-0.35015275133524659</v>
       </c>
       <c r="I36">
         <v>115.3540008544922</v>
       </c>
       <c r="J36">
-        <v>112.2534996032715</v>
+        <v>112.25349960327149</v>
       </c>
       <c r="K36">
         <v>105.2078001403809</v>
       </c>
       <c r="L36">
-        <v>88.56463764190674</v>
+        <v>88.564637641906742</v>
       </c>
       <c r="M36">
         <v>1.03</v>
       </c>
       <c r="N36">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -5384,7 +5414,7 @@
         <v>26.22</v>
       </c>
       <c r="AC36">
-        <v>35.95</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="AD36">
         <v>33.83</v>
@@ -5417,15 +5447,15 @@
         <v>367.79</v>
       </c>
       <c r="AN36">
-        <v>32.10807450937899</v>
+        <v>32.108074509378987</v>
       </c>
     </row>
     <row r="37" spans="1:40">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B37">
-        <v>90.63630880579011</v>
+        <v>90.636308805790108</v>
       </c>
       <c r="C37">
         <v>1756</v>
@@ -5437,25 +5467,25 @@
         <v>1.33</v>
       </c>
       <c r="F37">
-        <v>-0.3714062599945349</v>
+        <v>-0.37140625999453492</v>
       </c>
       <c r="G37">
         <v>1.34</v>
       </c>
       <c r="H37">
-        <v>-0.6896248776680844</v>
+        <v>-0.68962487766808445</v>
       </c>
       <c r="I37">
-        <v>46.69000091552734</v>
+        <v>46.690000915527342</v>
       </c>
       <c r="J37">
-        <v>46.01100063323975</v>
+        <v>46.011000633239753</v>
       </c>
       <c r="K37">
-        <v>43.9369002532959</v>
+        <v>43.936900253295903</v>
       </c>
       <c r="L37">
-        <v>36.13135932922363</v>
+        <v>36.131359329223628</v>
       </c>
       <c r="M37">
         <v>1.01</v>
@@ -5506,7 +5536,7 @@
         <v>116.32</v>
       </c>
       <c r="AD37">
-        <v>17.74</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="AE37">
         <v>167.16</v>
@@ -5540,11 +5570,11 @@
       </c>
     </row>
     <row r="38" spans="1:40">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B38">
-        <v>90.00301568154403</v>
+        <v>90.003015681544028</v>
       </c>
       <c r="C38">
         <v>790</v>
@@ -5556,22 +5586,22 @@
         <v>1.36</v>
       </c>
       <c r="F38">
-        <v>-0.3657687414192295</v>
+        <v>-0.36576874141922949</v>
       </c>
       <c r="G38">
         <v>1.39</v>
       </c>
       <c r="H38">
-        <v>-0.6741943264711374</v>
+        <v>-0.67419432647113742</v>
       </c>
       <c r="I38">
-        <v>49.22800064086914</v>
+        <v>49.228000640869141</v>
       </c>
       <c r="J38">
-        <v>48.65450057983399</v>
+        <v>48.654500579833993</v>
       </c>
       <c r="K38">
-        <v>46.65300010681153</v>
+        <v>46.653000106811533</v>
       </c>
       <c r="L38">
         <v>38.83916393280029</v>
@@ -5625,7 +5655,7 @@
         <v>116.32</v>
       </c>
       <c r="AD38">
-        <v>17.74</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="AE38">
         <v>167.16</v>
@@ -5652,7 +5682,7 @@
         <v>3.73</v>
       </c>
       <c r="AM38">
-        <v>-8.800000000000001</v>
+        <v>-8.8000000000000007</v>
       </c>
       <c r="AN38">
         <v>32.02409306684126</v>
@@ -5663,7 +5693,7 @@
         <v>77</v>
       </c>
       <c r="B39">
-        <v>95.59710494571773</v>
+        <v>95.597104945717732</v>
       </c>
       <c r="C39">
         <v>82</v>
@@ -5675,7 +5705,7 @@
         <v>6.82</v>
       </c>
       <c r="F39">
-        <v>0.6602596392863379</v>
+        <v>0.66025963928633791</v>
       </c>
       <c r="G39">
         <v>4.29</v>
@@ -5684,16 +5714,16 @@
         <v>0.220777642951799</v>
       </c>
       <c r="I39">
-        <v>231.7779998779297</v>
+        <v>231.77799987792969</v>
       </c>
       <c r="J39">
         <v>224.6883476257324</v>
       </c>
       <c r="K39">
-        <v>192.1588854980469</v>
+        <v>192.15888549804691</v>
       </c>
       <c r="L39">
-        <v>162.2560387802124</v>
+        <v>162.25603878021241</v>
       </c>
       <c r="M39">
         <v>1.03</v>
@@ -5732,7 +5762,7 @@
         <v>251.21</v>
       </c>
       <c r="Z39">
-        <v>1074.86</v>
+        <v>1074.8599999999999</v>
       </c>
       <c r="AA39">
         <v>13.91</v>
@@ -5753,7 +5783,7 @@
         <v>55.63</v>
       </c>
       <c r="AG39">
-        <v>-65.56999999999999</v>
+        <v>-65.569999999999993</v>
       </c>
       <c r="AH39" t="s">
         <v>158</v>
@@ -5774,7 +5804,7 @@
         <v>382.03</v>
       </c>
       <c r="AN39">
-        <v>30.84448603084208</v>
+        <v>30.844486030842081</v>
       </c>
     </row>
     <row r="40" spans="1:40">
@@ -5782,7 +5812,7 @@
         <v>78</v>
       </c>
       <c r="B40">
-        <v>94.11942098914355</v>
+        <v>94.119420989143549</v>
       </c>
       <c r="C40">
         <v>1322</v>
@@ -5794,25 +5824,25 @@
         <v>2.67</v>
       </c>
       <c r="F40">
-        <v>-0.1195970969642308</v>
+        <v>-0.11959709696423081</v>
       </c>
       <c r="G40">
         <v>5.36</v>
       </c>
       <c r="H40">
-        <v>0.5509914385664687</v>
+        <v>0.55099143856646871</v>
       </c>
       <c r="I40">
-        <v>54.96600036621093</v>
+        <v>54.966000366210928</v>
       </c>
       <c r="J40">
-        <v>54.78950004577636</v>
+        <v>54.789500045776357</v>
       </c>
       <c r="K40">
-        <v>51.83120002746582</v>
+        <v>51.831200027465819</v>
       </c>
       <c r="L40">
-        <v>36.56250003814697</v>
+        <v>36.562500038146972</v>
       </c>
       <c r="M40">
         <v>1</v>
@@ -5901,7 +5931,7 @@
         <v>79</v>
       </c>
       <c r="B41">
-        <v>90.51568154402895</v>
+        <v>90.515681544028951</v>
       </c>
       <c r="C41">
         <v>1413</v>
@@ -5913,25 +5943,25 @@
         <v>1.4</v>
       </c>
       <c r="F41">
-        <v>-0.3582520499854892</v>
+        <v>-0.35825204998548921</v>
       </c>
       <c r="G41">
         <v>1.74</v>
       </c>
       <c r="H41">
-        <v>-0.5661804680925071</v>
+        <v>-0.56618046809250711</v>
       </c>
       <c r="I41">
-        <v>535.5180053710938</v>
+        <v>535.51800537109375</v>
       </c>
       <c r="J41">
-        <v>534.6204986572266</v>
+        <v>534.62049865722656</v>
       </c>
       <c r="K41">
-        <v>533.1747991943359</v>
+        <v>533.17479919433595</v>
       </c>
       <c r="L41">
-        <v>462.4402998352051</v>
+        <v>462.44029983520511</v>
       </c>
       <c r="M41">
         <v>1</v>
@@ -5952,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U41" t="b">
         <v>1</v>
@@ -5973,7 +6003,7 @@
         <v>193.77</v>
       </c>
       <c r="AA41">
-        <v>9.710000000000001</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="AB41">
         <v>20.27</v>
@@ -6012,7 +6042,7 @@
         <v>26.77</v>
       </c>
       <c r="AN41">
-        <v>29.75677243615812</v>
+        <v>29.756772436158119</v>
       </c>
     </row>
     <row r="42" spans="1:40">
@@ -6020,7 +6050,7 @@
         <v>80</v>
       </c>
       <c r="B42">
-        <v>90.2593486127865</v>
+        <v>90.259348612786496</v>
       </c>
       <c r="C42">
         <v>1542</v>
@@ -6032,7 +6062,7 @@
         <v>1.05</v>
       </c>
       <c r="F42">
-        <v>-0.4240231000307177</v>
+        <v>-0.42402310003071769</v>
       </c>
       <c r="G42">
         <v>1.57</v>
@@ -6041,16 +6071,16 @@
         <v>-0.6186443421621276</v>
       </c>
       <c r="I42">
-        <v>73.12399902343751</v>
+        <v>73.123999023437506</v>
       </c>
       <c r="J42">
-        <v>72.89449958801269</v>
+        <v>72.894499588012692</v>
       </c>
       <c r="K42">
-        <v>71.96139991760253</v>
+        <v>71.961399917602535</v>
       </c>
       <c r="L42">
-        <v>58.1523307800293</v>
+        <v>58.152330780029303</v>
       </c>
       <c r="M42">
         <v>1</v>
@@ -6122,24 +6152,24 @@
         <v>231</v>
       </c>
       <c r="AK42">
-        <v>9.210000000000001</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="AL42">
-        <v>9.039999999999999</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="AM42">
         <v>-1.85</v>
       </c>
       <c r="AN42">
-        <v>28.26186195706586</v>
+        <v>28.261861957065861</v>
       </c>
     </row>
     <row r="43" spans="1:40">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B43">
-        <v>92.7925211097708</v>
+        <v>92.792521109770803</v>
       </c>
       <c r="C43">
         <v>1039</v>
@@ -6157,16 +6187,16 @@
         <v>2.27</v>
       </c>
       <c r="H43">
-        <v>-0.402616625404867</v>
+        <v>-0.40261662540486698</v>
       </c>
       <c r="I43">
-        <v>206.5760009765625</v>
+        <v>206.57600097656251</v>
       </c>
       <c r="J43">
         <v>206.5264976501465</v>
       </c>
       <c r="K43">
-        <v>191.4769989013672</v>
+        <v>191.47699890136721</v>
       </c>
       <c r="L43">
         <v>163.4166329193115</v>
@@ -6190,7 +6220,7 @@
         <v>2</v>
       </c>
       <c r="T43">
-        <v>3.888888888888889</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="U43" t="b">
         <v>1</v>
@@ -6217,7 +6247,7 @@
         <v>14.65</v>
       </c>
       <c r="AC43">
-        <v>39.52</v>
+        <v>39.520000000000003</v>
       </c>
       <c r="AD43">
         <v>43.57</v>
@@ -6229,7 +6259,7 @@
         <v>-7.35</v>
       </c>
       <c r="AG43">
-        <v>-67.73999999999999</v>
+        <v>-67.739999999999995</v>
       </c>
       <c r="AH43" t="s">
         <v>173</v>
@@ -6250,7 +6280,7 @@
         <v>12.17</v>
       </c>
       <c r="AN43">
-        <v>27.98434502746725</v>
+        <v>27.984345027467249</v>
       </c>
     </row>
     <row r="44" spans="1:40">
@@ -6258,7 +6288,7 @@
         <v>82</v>
       </c>
       <c r="B44">
-        <v>96.2605548854041</v>
+        <v>96.260554885404105</v>
       </c>
       <c r="C44">
         <v>74</v>
@@ -6270,31 +6300,31 @@
         <v>8.91</v>
       </c>
       <c r="F44">
-        <v>1.053006766699275</v>
+        <v>1.0530067666992751</v>
       </c>
       <c r="G44">
         <v>7.9</v>
       </c>
       <c r="H44">
-        <v>1.334863439371386</v>
+        <v>1.3348634393713861</v>
       </c>
       <c r="I44">
-        <v>7.173000144958496</v>
+        <v>7.1730001449584959</v>
       </c>
       <c r="J44">
-        <v>7.182750034332275</v>
+        <v>7.1827500343322752</v>
       </c>
       <c r="K44">
-        <v>6.516199998855591</v>
+        <v>6.5161999988555914</v>
       </c>
       <c r="L44">
-        <v>4.440199998617172</v>
+        <v>4.4401999986171719</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -6339,7 +6369,7 @@
         <v>5.43</v>
       </c>
       <c r="AD44">
-        <v>-35.98</v>
+        <v>-35.979999999999997</v>
       </c>
       <c r="AE44">
         <v>-8.33</v>
@@ -6369,15 +6399,15 @@
         <v>4.26</v>
       </c>
       <c r="AN44">
-        <v>27.60167201220351</v>
+        <v>27.601672012203512</v>
       </c>
     </row>
     <row r="45" spans="1:40">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B45">
-        <v>95.73281061519904</v>
+        <v>95.732810615199043</v>
       </c>
       <c r="C45">
         <v>1455</v>
@@ -6389,7 +6419,7 @@
         <v>1.65</v>
       </c>
       <c r="F45">
-        <v>-0.3112727285246115</v>
+        <v>-0.31127272852461152</v>
       </c>
       <c r="G45">
         <v>2.16</v>
@@ -6398,16 +6428,16 @@
         <v>-0.4365638380381508</v>
       </c>
       <c r="I45">
-        <v>187.6700012207031</v>
+        <v>187.67000122070311</v>
       </c>
       <c r="J45">
         <v>180.5679992675781</v>
       </c>
       <c r="K45">
-        <v>178.0304739379883</v>
+        <v>178.03047393798829</v>
       </c>
       <c r="L45">
-        <v>137.6887182235718</v>
+        <v>137.68871822357181</v>
       </c>
       <c r="M45">
         <v>1.04</v>
@@ -6464,7 +6494,7 @@
         <v>0.6</v>
       </c>
       <c r="AF45">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AG45">
         <v>8.67</v>
@@ -6488,15 +6518,15 @@
         <v>7.8</v>
       </c>
       <c r="AN45">
-        <v>27.57301719423034</v>
+        <v>27.573017194230339</v>
       </c>
     </row>
     <row r="46" spans="1:40">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B46">
-        <v>91.22436670687576</v>
+        <v>91.224366706875756</v>
       </c>
       <c r="C46">
         <v>2090</v>
@@ -6508,25 +6538,25 @@
         <v>1.52</v>
       </c>
       <c r="F46">
-        <v>-0.3357019756842679</v>
+        <v>-0.33570197568426791</v>
       </c>
       <c r="G46">
         <v>1.84</v>
       </c>
       <c r="H46">
-        <v>-0.5353193656986127</v>
+        <v>-0.53531936569861271</v>
       </c>
       <c r="I46">
-        <v>238.9160034179687</v>
+        <v>238.91600341796871</v>
       </c>
       <c r="J46">
-        <v>230.7057487487793</v>
+        <v>230.70574874877931</v>
       </c>
       <c r="K46">
         <v>220.5412057495117</v>
       </c>
       <c r="L46">
-        <v>186.2534450531006</v>
+        <v>186.25344505310059</v>
       </c>
       <c r="M46">
         <v>1.04</v>
@@ -6586,7 +6616,7 @@
         <v>89.36</v>
       </c>
       <c r="AG46">
-        <v>-66.81999999999999</v>
+        <v>-66.819999999999993</v>
       </c>
       <c r="AH46" t="s">
         <v>177</v>
@@ -6607,7 +6637,7 @@
         <v>24</v>
       </c>
       <c r="AN46">
-        <v>23.13567603923404</v>
+        <v>23.135676039234038</v>
       </c>
     </row>
     <row r="47" spans="1:40">
@@ -6615,7 +6645,7 @@
         <v>85</v>
       </c>
       <c r="B47">
-        <v>91.79734620024126</v>
+        <v>91.797346200241265</v>
       </c>
       <c r="C47">
         <v>712</v>
@@ -6627,25 +6657,25 @@
         <v>1.36</v>
       </c>
       <c r="F47">
-        <v>-0.3657687414192295</v>
+        <v>-0.36576874141922949</v>
       </c>
       <c r="G47">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H47">
-        <v>-0.4705110506714347</v>
+        <v>-0.47051105067143473</v>
       </c>
       <c r="I47">
-        <v>40.28200073242188</v>
+        <v>40.282000732421878</v>
       </c>
       <c r="J47">
-        <v>38.86000022888184</v>
+        <v>38.860000228881837</v>
       </c>
       <c r="K47">
-        <v>38.43159996032715</v>
+        <v>38.431599960327148</v>
       </c>
       <c r="L47">
-        <v>32.69360005378723</v>
+        <v>32.693600053787229</v>
       </c>
       <c r="M47">
         <v>1.04</v>
@@ -6696,7 +6726,7 @@
         <v>5.13</v>
       </c>
       <c r="AD47">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="AE47">
         <v>54.29</v>
@@ -6726,7 +6756,7 @@
         <v>33.65</v>
       </c>
       <c r="AN47">
-        <v>22.66954053245709</v>
+        <v>22.669540532457091</v>
       </c>
     </row>
     <row r="48" spans="1:40">
@@ -6734,7 +6764,7 @@
         <v>86</v>
       </c>
       <c r="B48">
-        <v>94.34559710494572</v>
+        <v>94.345597104945725</v>
       </c>
       <c r="C48">
         <v>1267</v>
@@ -6746,31 +6776,31 @@
         <v>2.38</v>
       </c>
       <c r="F48">
-        <v>-0.1740931098588488</v>
+        <v>-0.17409310985884879</v>
       </c>
       <c r="G48">
         <v>4.17</v>
       </c>
       <c r="H48">
-        <v>0.1837443200791257</v>
+        <v>0.18374432007912569</v>
       </c>
       <c r="I48">
-        <v>194.1059997558594</v>
+        <v>194.10599975585939</v>
       </c>
       <c r="J48">
         <v>189.8030006408691</v>
       </c>
       <c r="K48">
-        <v>167.3426010131836</v>
+        <v>167.34260101318361</v>
       </c>
       <c r="L48">
-        <v>150.9094410705567</v>
+        <v>150.90944107055671</v>
       </c>
       <c r="M48">
         <v>1.02</v>
       </c>
       <c r="N48">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -6836,10 +6866,10 @@
         <v>235</v>
       </c>
       <c r="AK48">
-        <v>8.460000000000001</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="AL48">
-        <v>8.130000000000001</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="AM48">
         <v>-3.9</v>
@@ -6853,7 +6883,7 @@
         <v>87</v>
       </c>
       <c r="B49">
-        <v>90.50060313630881</v>
+        <v>90.500603136308811</v>
       </c>
       <c r="C49">
         <v>194</v>
@@ -6865,13 +6895,13 @@
         <v>1.3</v>
       </c>
       <c r="F49">
-        <v>-0.3770437785698401</v>
+        <v>-0.37704377856984012</v>
       </c>
       <c r="G49">
         <v>1.47</v>
       </c>
       <c r="H49">
-        <v>-0.6495054445560219</v>
+        <v>-0.64950544455602188</v>
       </c>
       <c r="I49">
         <v>28.0620002746582</v>
@@ -6883,7 +6913,7 @@
         <v>26.96137802124024</v>
       </c>
       <c r="L49">
-        <v>21.82576705932617</v>
+        <v>21.825767059326171</v>
       </c>
       <c r="M49">
         <v>1.03</v>
@@ -6925,7 +6955,7 @@
         <v>62.85</v>
       </c>
       <c r="AA49">
-        <v>9.869999999999999</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="AB49">
         <v>10.45</v>
@@ -6955,7 +6985,7 @@
         <v>217</v>
       </c>
       <c r="AK49">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AL49">
         <v>1.26</v>
@@ -6964,7 +6994,7 @@
         <v>11.5</v>
       </c>
       <c r="AN49">
-        <v>22.32082536814048</v>
+        <v>22.320825368140479</v>
       </c>
     </row>
     <row r="50" spans="1:40">
@@ -6972,7 +7002,7 @@
         <v>88</v>
       </c>
       <c r="B50">
-        <v>91.29975874547648</v>
+        <v>91.299758745476481</v>
       </c>
       <c r="C50">
         <v>1738</v>
@@ -6984,22 +7014,22 @@
         <v>2.06</v>
       </c>
       <c r="F50">
-        <v>-0.2342266413287722</v>
+        <v>-0.23422664132877219</v>
       </c>
       <c r="G50">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="H50">
-        <v>-0.4828554916289924</v>
+        <v>-0.48285549162899238</v>
       </c>
       <c r="I50">
-        <v>229.0359985351562</v>
+        <v>229.03599853515621</v>
       </c>
       <c r="J50">
-        <v>225.0442321777344</v>
+        <v>225.04423217773439</v>
       </c>
       <c r="K50">
-        <v>211.6632089233399</v>
+        <v>211.66320892333991</v>
       </c>
       <c r="L50">
         <v>209.3467724609375</v>
@@ -7083,7 +7113,7 @@
         <v>5.93</v>
       </c>
       <c r="AN50">
-        <v>19.28132339300524</v>
+        <v>19.281323393005241</v>
       </c>
     </row>
     <row r="51" spans="1:40">
@@ -7091,40 +7121,40 @@
         <v>89</v>
       </c>
       <c r="B51">
-        <v>96.18516284680338</v>
+        <v>96.185162846803379</v>
       </c>
       <c r="C51">
         <v>2593</v>
       </c>
       <c r="D51">
-        <v>32.77</v>
+        <v>32.770000000000003</v>
       </c>
       <c r="E51">
         <v>3.26</v>
       </c>
       <c r="F51">
-        <v>-0.008725898316559627</v>
+        <v>-8.7258983165596268E-3</v>
       </c>
       <c r="G51">
         <v>2.81</v>
       </c>
       <c r="H51">
-        <v>-0.2359666724778375</v>
+        <v>-0.23596667247783751</v>
       </c>
       <c r="I51">
-        <v>32.74200057983398</v>
+        <v>32.742000579833977</v>
       </c>
       <c r="J51">
-        <v>30.0105001449585</v>
+        <v>30.010500144958499</v>
       </c>
       <c r="K51">
-        <v>27.81820007324219</v>
+        <v>27.818200073242188</v>
       </c>
       <c r="L51">
-        <v>20.86644999980927</v>
+        <v>20.866449999809269</v>
       </c>
       <c r="M51">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N51">
         <v>1.18</v>
@@ -7157,7 +7187,7 @@
         <v>11.81</v>
       </c>
       <c r="Y51">
-        <v>34.37</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="Z51">
         <v>5.81</v>
@@ -7169,7 +7199,7 @@
         <v>6100</v>
       </c>
       <c r="AC51">
-        <v>256.29</v>
+        <v>256.29000000000002</v>
       </c>
       <c r="AD51">
         <v>9.09</v>
@@ -7199,10 +7229,10 @@
         <v>1.8</v>
       </c>
       <c r="AM51">
-        <v>85.56999999999999</v>
+        <v>85.57</v>
       </c>
       <c r="AN51">
-        <v>90.94287614602163</v>
+        <v>90.942876146021632</v>
       </c>
     </row>
     <row r="52" spans="1:40">
@@ -7210,7 +7240,7 @@
         <v>90</v>
       </c>
       <c r="B52">
-        <v>97.05971049457177</v>
+        <v>97.059710494571775</v>
       </c>
       <c r="C52">
         <v>1569</v>
@@ -7225,22 +7255,22 @@
         <v>-0.159059726991368</v>
       </c>
       <c r="G52">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H52">
-        <v>0.4707525723423431</v>
+        <v>0.47075257234234308</v>
       </c>
       <c r="I52">
-        <v>22.56800003051758</v>
+        <v>22.568000030517581</v>
       </c>
       <c r="J52">
-        <v>22.75606079101562</v>
+        <v>22.756060791015621</v>
       </c>
       <c r="K52">
-        <v>21.53616296768189</v>
+        <v>21.536162967681889</v>
       </c>
       <c r="L52">
-        <v>15.27871369838715</v>
+        <v>15.278713698387151</v>
       </c>
       <c r="M52">
         <v>0.99</v>
@@ -7294,7 +7324,7 @@
         <v>-21.89</v>
       </c>
       <c r="AE52">
-        <v>64.70999999999999</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="AF52">
         <v>189.47</v>
@@ -7321,7 +7351,7 @@
         <v>250.57</v>
       </c>
       <c r="AN52">
-        <v>75.60635331841249</v>
+        <v>75.606353318412488</v>
       </c>
     </row>
     <row r="53" spans="1:40">
@@ -7329,7 +7359,7 @@
         <v>91</v>
       </c>
       <c r="B53">
-        <v>92.71712907117008</v>
+        <v>92.717129071170078</v>
       </c>
       <c r="C53">
         <v>589</v>
@@ -7341,25 +7371,25 @@
         <v>2.06</v>
       </c>
       <c r="F53">
-        <v>-0.2342266413287722</v>
+        <v>-0.23422664132877219</v>
       </c>
       <c r="G53">
         <v>3.03</v>
       </c>
       <c r="H53">
-        <v>-0.16807224721127</v>
+        <v>-0.16807224721127001</v>
       </c>
       <c r="I53">
-        <v>37.4120002746582</v>
+        <v>37.412000274658197</v>
       </c>
       <c r="J53">
-        <v>35.58449993133545</v>
+        <v>35.584499931335451</v>
       </c>
       <c r="K53">
-        <v>31.81899997711182</v>
+        <v>31.818999977111819</v>
       </c>
       <c r="L53">
-        <v>26.03614995956421</v>
+        <v>26.036149959564209</v>
       </c>
       <c r="M53">
         <v>1.05</v>
@@ -7380,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U53" t="b">
         <v>0</v>
@@ -7392,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="X53">
-        <v>19.24</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="Y53">
         <v>39.47</v>
@@ -7407,7 +7437,7 @@
         <v>1153.08</v>
       </c>
       <c r="AC53">
-        <v>70.04000000000001</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="AD53">
         <v>-8.57</v>
@@ -7440,7 +7470,7 @@
         <v>455.26</v>
       </c>
       <c r="AN53">
-        <v>70.80342272643834</v>
+        <v>70.803422726438342</v>
       </c>
     </row>
     <row r="54" spans="1:40">
@@ -7457,16 +7487,16 @@
         <v>111.04</v>
       </c>
       <c r="E54">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="F54">
-        <v>-0.2436225056209478</v>
+        <v>-0.24362250562094781</v>
       </c>
       <c r="G54">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H54">
-        <v>-0.4303916175593719</v>
+        <v>-0.43039161755937189</v>
       </c>
       <c r="I54">
         <v>106.2400009155273</v>
@@ -7478,7 +7508,7 @@
         <v>106.935</v>
       </c>
       <c r="L54">
-        <v>85.33110004425049</v>
+        <v>85.331100044250491</v>
       </c>
       <c r="M54">
         <v>1.02</v>
@@ -7517,16 +7547,16 @@
         <v>117.51</v>
       </c>
       <c r="Z54">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AA54">
-        <v>-32.02</v>
+        <v>-32.020000000000003</v>
       </c>
       <c r="AB54">
         <v>835.28</v>
       </c>
       <c r="AC54">
-        <v>291.46</v>
+        <v>291.45999999999998</v>
       </c>
       <c r="AD54">
         <v>10.93</v>
@@ -7559,7 +7589,7 @@
         <v>42.98</v>
       </c>
       <c r="AN54">
-        <v>70.23618510063982</v>
+        <v>70.236185100639815</v>
       </c>
     </row>
     <row r="55" spans="1:40">
@@ -7567,7 +7597,7 @@
         <v>93</v>
       </c>
       <c r="B55">
-        <v>98.35645355850421</v>
+        <v>98.356453558504214</v>
       </c>
       <c r="C55">
         <v>1914</v>
@@ -7591,7 +7621,7 @@
         <v>214.8649963378906</v>
       </c>
       <c r="J55">
-        <v>206.2217498779297</v>
+        <v>206.22174987792971</v>
       </c>
       <c r="K55">
         <v>204.5620999145508</v>
@@ -7675,7 +7705,7 @@
         <v>6.99</v>
       </c>
       <c r="AN55">
-        <v>67.07966874599198</v>
+        <v>67.079668745991981</v>
       </c>
     </row>
     <row r="56" spans="1:40">
@@ -7683,7 +7713,7 @@
         <v>94</v>
       </c>
       <c r="B56">
-        <v>93.68214716525934</v>
+        <v>93.682147165259337</v>
       </c>
       <c r="C56">
         <v>2938</v>
@@ -7695,25 +7725,25 @@
         <v>3.02</v>
       </c>
       <c r="F56">
-        <v>-0.05382604691900211</v>
+        <v>-5.3826046919002113E-2</v>
       </c>
       <c r="G56">
         <v>3.13</v>
       </c>
       <c r="H56">
-        <v>-0.1372111448173756</v>
+        <v>-0.13721114481737559</v>
       </c>
       <c r="I56">
-        <v>22.87599983215332</v>
+        <v>22.875999832153319</v>
       </c>
       <c r="J56">
-        <v>22.52699995040894</v>
+        <v>22.526999950408939</v>
       </c>
       <c r="K56">
         <v>22.03880001068115</v>
       </c>
       <c r="L56">
-        <v>18.93920000076294</v>
+        <v>18.939200000762941</v>
       </c>
       <c r="M56">
         <v>1.02</v>
@@ -7794,7 +7824,7 @@
         <v>370</v>
       </c>
       <c r="AN56">
-        <v>65.01268244767921</v>
+        <v>65.012682447679211</v>
       </c>
     </row>
     <row r="57" spans="1:40">
@@ -7802,7 +7832,7 @@
         <v>95</v>
       </c>
       <c r="B57">
-        <v>94.22496984318455</v>
+        <v>94.224969843184553</v>
       </c>
       <c r="C57">
         <v>474</v>
@@ -7814,25 +7844,25 @@
         <v>1.59</v>
       </c>
       <c r="F57">
-        <v>-0.3225477656752221</v>
+        <v>-0.32254776567522209</v>
       </c>
       <c r="G57">
         <v>3.09</v>
       </c>
       <c r="H57">
-        <v>-0.1495555857749334</v>
+        <v>-0.14955558577493339</v>
       </c>
       <c r="I57">
-        <v>8.244000053405761</v>
+        <v>8.2440000534057614</v>
       </c>
       <c r="J57">
-        <v>8.3375</v>
+        <v>8.3375000000000004</v>
       </c>
       <c r="K57">
-        <v>8.164399986267091</v>
+        <v>8.1643999862670906</v>
       </c>
       <c r="L57">
-        <v>6.294900000095367</v>
+        <v>6.2949000000953674</v>
       </c>
       <c r="M57">
         <v>0.99</v>
@@ -7913,7 +7943,7 @@
         <v>345.83</v>
       </c>
       <c r="AN57">
-        <v>64.82160378816751</v>
+        <v>64.821603788167508</v>
       </c>
     </row>
     <row r="58" spans="1:40">
@@ -7921,7 +7951,7 @@
         <v>96</v>
       </c>
       <c r="B58">
-        <v>90.8021712907117</v>
+        <v>90.802171290711698</v>
       </c>
       <c r="C58">
         <v>2134</v>
@@ -7933,31 +7963,31 @@
         <v>3.56</v>
       </c>
       <c r="F58">
-        <v>0.04764928743649358</v>
+        <v>4.7649287436493583E-2</v>
       </c>
       <c r="G58">
         <v>2.59</v>
       </c>
       <c r="H58">
-        <v>-0.3038610977444052</v>
+        <v>-0.30386109774440517</v>
       </c>
       <c r="I58">
-        <v>15.62400016784668</v>
+        <v>15.624000167846679</v>
       </c>
       <c r="J58">
-        <v>14.78449997901916</v>
+        <v>14.784499979019159</v>
       </c>
       <c r="K58">
         <v>13.63199996948242</v>
       </c>
       <c r="L58">
-        <v>10.57625000476837</v>
+        <v>10.576250004768371</v>
       </c>
       <c r="M58">
         <v>1.06</v>
       </c>
       <c r="N58">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P58">
         <v>1</v>
@@ -7972,7 +8002,7 @@
         <v>2</v>
       </c>
       <c r="T58">
-        <v>7.222222222222223</v>
+        <v>7.2222222222222232</v>
       </c>
       <c r="U58" t="b">
         <v>0</v>
@@ -7987,10 +8017,10 @@
         <v>7.07</v>
       </c>
       <c r="Y58">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="Z58">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AA58">
         <v>-3.51</v>
@@ -8011,7 +8041,7 @@
         <v>-78.05</v>
       </c>
       <c r="AG58">
-        <v>-94.29000000000001</v>
+        <v>-94.29</v>
       </c>
       <c r="AH58" t="s">
         <v>185</v>
@@ -8032,7 +8062,7 @@
         <v>-22.13</v>
       </c>
       <c r="AN58">
-        <v>64.2397952859527</v>
+        <v>64.239795285952695</v>
       </c>
     </row>
     <row r="59" spans="1:40">
@@ -8040,7 +8070,7 @@
         <v>97</v>
       </c>
       <c r="B59">
-        <v>94.31544028950543</v>
+        <v>94.315440289505432</v>
       </c>
       <c r="C59">
         <v>1878</v>
@@ -8049,10 +8079,10 @@
         <v>104.73</v>
       </c>
       <c r="E59">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F59">
-        <v>-0.2041598755938105</v>
+        <v>-0.20415987559381049</v>
       </c>
       <c r="G59">
         <v>1.71</v>
@@ -8067,7 +8097,7 @@
         <v>104.5744998931885</v>
       </c>
       <c r="K59">
-        <v>97.85284912109375</v>
+        <v>97.852849121093755</v>
       </c>
       <c r="L59">
         <v>73.83936985015869</v>
@@ -8091,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="T59">
-        <v>16.11111111111111</v>
+        <v>16.111111111111111</v>
       </c>
       <c r="U59" t="b">
         <v>0</v>
@@ -8118,7 +8148,7 @@
         <v>169.95</v>
       </c>
       <c r="AC59">
-        <v>1185.09</v>
+        <v>1185.0899999999999</v>
       </c>
       <c r="AD59">
         <v>34.26</v>
@@ -8148,10 +8178,10 @@
         <v>3.22</v>
       </c>
       <c r="AM59">
-        <v>-74.95999999999999</v>
+        <v>-74.959999999999994</v>
       </c>
       <c r="AN59">
-        <v>61.57389366849652</v>
+        <v>61.573893668496517</v>
       </c>
     </row>
     <row r="60" spans="1:40">
@@ -8165,37 +8195,37 @@
         <v>1409</v>
       </c>
       <c r="D60">
-        <v>67.59999999999999</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="E60">
         <v>3.02</v>
       </c>
       <c r="F60">
-        <v>-0.05382604691900211</v>
+        <v>-5.3826046919002113E-2</v>
       </c>
       <c r="G60">
         <v>4.01</v>
       </c>
       <c r="H60">
-        <v>0.1343665562488947</v>
+        <v>0.13436655624889471</v>
       </c>
       <c r="I60">
-        <v>65.69399871826172</v>
+        <v>65.693998718261724</v>
       </c>
       <c r="J60">
-        <v>64.45699977874756</v>
+        <v>64.456999778747559</v>
       </c>
       <c r="K60">
-        <v>57.67759986877441</v>
+        <v>57.677599868774408</v>
       </c>
       <c r="L60">
-        <v>41.84244998931885</v>
+        <v>41.842449989318851</v>
       </c>
       <c r="M60">
         <v>1.02</v>
       </c>
       <c r="N60">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -8249,7 +8279,7 @@
         <v>-625</v>
       </c>
       <c r="AG60">
-        <v>96.40000000000001</v>
+        <v>96.4</v>
       </c>
       <c r="AH60" t="s">
         <v>187</v>
@@ -8270,7 +8300,7 @@
         <v>112.74</v>
       </c>
       <c r="AN60">
-        <v>61.36318858601847</v>
+        <v>61.363188586018467</v>
       </c>
     </row>
     <row r="61" spans="1:40">
@@ -8278,7 +8308,7 @@
         <v>99</v>
       </c>
       <c r="B61">
-        <v>97.33112183353438</v>
+        <v>97.331121833534382</v>
       </c>
       <c r="C61">
         <v>2624</v>
@@ -8290,25 +8320,25 @@
         <v>2.89</v>
       </c>
       <c r="F61">
-        <v>-0.07825529407865844</v>
+        <v>-7.8255294078658444E-2</v>
       </c>
       <c r="G61">
         <v>2.8</v>
       </c>
       <c r="H61">
-        <v>-0.239052782717227</v>
+        <v>-0.23905278271722699</v>
       </c>
       <c r="I61">
-        <v>14.62599983215332</v>
+        <v>14.625999832153321</v>
       </c>
       <c r="J61">
-        <v>13.99749989509582</v>
+        <v>13.997499895095819</v>
       </c>
       <c r="K61">
         <v>12.26559989929199</v>
       </c>
       <c r="L61">
-        <v>9.064049971103668</v>
+        <v>9.0640499711036675</v>
       </c>
       <c r="M61">
         <v>1.04</v>
@@ -8389,7 +8419,7 @@
         <v>330.77</v>
       </c>
       <c r="AN61">
-        <v>61.34145770235383</v>
+        <v>61.341457702353829</v>
       </c>
     </row>
     <row r="62" spans="1:40">
@@ -8397,7 +8427,7 @@
         <v>100</v>
       </c>
       <c r="B62">
-        <v>93.27503015681545</v>
+        <v>93.275030156815447</v>
       </c>
       <c r="C62">
         <v>2181</v>
@@ -8409,16 +8439,16 @@
         <v>5.15</v>
       </c>
       <c r="F62">
-        <v>0.3464377719276753</v>
+        <v>0.34643777192767528</v>
       </c>
       <c r="G62">
         <v>3.63</v>
       </c>
       <c r="H62">
-        <v>0.01709436715209618</v>
+        <v>1.7094367152096179E-2</v>
       </c>
       <c r="I62">
-        <v>28.3560001373291</v>
+        <v>28.356000137329101</v>
       </c>
       <c r="J62">
         <v>27.60949983596802</v>
@@ -8427,13 +8457,13 @@
         <v>24.54559997558594</v>
       </c>
       <c r="L62">
-        <v>16.42995000362396</v>
+        <v>16.429950003623961</v>
       </c>
       <c r="M62">
         <v>1.03</v>
       </c>
       <c r="N62">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -8463,7 +8493,7 @@
         <v>8.58</v>
       </c>
       <c r="Y62">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="Z62">
         <v>1.73</v>
@@ -8481,7 +8511,7 @@
         <v>-5.66</v>
       </c>
       <c r="AE62">
-        <v>-85.29000000000001</v>
+        <v>-85.29</v>
       </c>
       <c r="AF62">
         <v>-36</v>
@@ -8508,7 +8538,7 @@
         <v>166.24</v>
       </c>
       <c r="AN62">
-        <v>60.21538188378956</v>
+        <v>60.215381883789561</v>
       </c>
     </row>
     <row r="63" spans="1:40">
@@ -8516,7 +8546,7 @@
         <v>101</v>
       </c>
       <c r="B63">
-        <v>91.42038600723762</v>
+        <v>91.420386007237624</v>
       </c>
       <c r="C63">
         <v>2844</v>
@@ -8528,22 +8558,22 @@
         <v>1.84</v>
       </c>
       <c r="F63">
-        <v>-0.2755684442143445</v>
+        <v>-0.27556844421434451</v>
       </c>
       <c r="G63">
         <v>2.46</v>
       </c>
       <c r="H63">
-        <v>-0.3439805308564678</v>
+        <v>-0.34398053085646779</v>
       </c>
       <c r="I63">
-        <v>57.56600036621094</v>
+        <v>57.566000366210943</v>
       </c>
       <c r="J63">
-        <v>56.91000003814698</v>
+        <v>56.910000038146983</v>
       </c>
       <c r="K63">
-        <v>54.74520011901856</v>
+        <v>54.745200119018563</v>
       </c>
       <c r="L63">
         <v>48.72875003814697</v>
@@ -8588,13 +8618,13 @@
         <v>2.94</v>
       </c>
       <c r="AA63">
-        <v>19.85</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="AB63">
         <v>275.98</v>
       </c>
       <c r="AC63">
-        <v>76.04000000000001</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="AD63">
         <v>1.54</v>
@@ -8627,7 +8657,7 @@
         <v>500</v>
       </c>
       <c r="AN63">
-        <v>56.79307127939545</v>
+        <v>56.793071279395448</v>
       </c>
     </row>
     <row r="64" spans="1:40">
@@ -8635,7 +8665,7 @@
         <v>102</v>
       </c>
       <c r="B64">
-        <v>94.27020506634499</v>
+        <v>94.270205066344985</v>
       </c>
       <c r="C64">
         <v>1752</v>
@@ -8644,22 +8674,22 @@
         <v>17.32</v>
       </c>
       <c r="E64">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F64">
-        <v>-0.2041598755938105</v>
+        <v>-0.20415987559381049</v>
       </c>
       <c r="G64">
         <v>2.39</v>
       </c>
       <c r="H64">
-        <v>-0.3655833025321938</v>
+        <v>-0.36558330253219379</v>
       </c>
       <c r="I64">
-        <v>17.61399993896485</v>
+        <v>17.613999938964849</v>
       </c>
       <c r="J64">
-        <v>17.16199984550476</v>
+        <v>17.161999845504759</v>
       </c>
       <c r="K64">
         <v>15.62919992446899</v>
@@ -8671,7 +8701,7 @@
         <v>1.03</v>
       </c>
       <c r="N64">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -8701,7 +8731,7 @@
         <v>7.93</v>
       </c>
       <c r="Y64">
-        <v>18.42</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="Z64">
         <v>3.06</v>
@@ -8754,7 +8784,7 @@
         <v>103</v>
       </c>
       <c r="B65">
-        <v>96.41133896260556</v>
+        <v>96.411338962605555</v>
       </c>
       <c r="C65">
         <v>2563</v>
@@ -8766,31 +8796,31 @@
         <v>1.51</v>
       </c>
       <c r="F65">
-        <v>-0.337581148542703</v>
+        <v>-0.33758114854270299</v>
       </c>
       <c r="G65">
         <v>1.91</v>
       </c>
       <c r="H65">
-        <v>-0.5137165940228867</v>
+        <v>-0.51371659402288672</v>
       </c>
       <c r="I65">
         <v>10.24799995422363</v>
       </c>
       <c r="J65">
-        <v>9.799499940872192</v>
+        <v>9.7994999408721917</v>
       </c>
       <c r="K65">
-        <v>8.818999938964843</v>
+        <v>8.8189999389648435</v>
       </c>
       <c r="L65">
-        <v>6.430832622051239</v>
+        <v>6.4308326220512386</v>
       </c>
       <c r="M65">
         <v>1.05</v>
       </c>
       <c r="N65">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -8805,7 +8835,7 @@
         <v>5</v>
       </c>
       <c r="T65">
-        <v>8.333333333333332</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="U65" t="b">
         <v>0</v>
@@ -8817,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="X65">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="Y65">
         <v>10.52</v>
@@ -8829,7 +8859,7 @@
         <v>155</v>
       </c>
       <c r="AB65">
-        <v>135.92</v>
+        <v>135.91999999999999</v>
       </c>
       <c r="AC65">
         <v>604.37</v>
@@ -8844,7 +8874,7 @@
         <v>126.67</v>
       </c>
       <c r="AG65">
-        <v>80.18000000000001</v>
+        <v>80.180000000000007</v>
       </c>
       <c r="AH65" t="s">
         <v>166</v>
@@ -8873,7 +8903,7 @@
         <v>104</v>
       </c>
       <c r="B66">
-        <v>92.12907117008444</v>
+        <v>92.129071170084444</v>
       </c>
       <c r="C66">
         <v>393</v>
@@ -8888,13 +8918,13 @@
         <v>0.2224123632709584</v>
       </c>
       <c r="G66">
-        <v>9.029999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="H66">
         <v>1.683593896422392</v>
       </c>
       <c r="I66">
-        <v>24.52199974060058</v>
+        <v>24.521999740600581</v>
       </c>
       <c r="J66">
         <v>24.09699983596802</v>
@@ -8924,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="T66">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U66" t="b">
         <v>0</v>
@@ -8992,7 +9022,7 @@
         <v>105</v>
       </c>
       <c r="B67">
-        <v>98.65802171290711</v>
+        <v>98.658021712907114</v>
       </c>
       <c r="C67">
         <v>981</v>
@@ -9010,10 +9040,10 @@
         <v>3.03</v>
       </c>
       <c r="H67">
-        <v>-0.16807224721127</v>
+        <v>-0.16807224721127001</v>
       </c>
       <c r="I67">
-        <v>14.30399990081787</v>
+        <v>14.303999900817869</v>
       </c>
       <c r="J67">
         <v>13.77749991416931</v>
@@ -9028,7 +9058,7 @@
         <v>1.04</v>
       </c>
       <c r="N67">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -9103,7 +9133,7 @@
         <v>1900</v>
       </c>
       <c r="AN67">
-        <v>55.27512943947821</v>
+        <v>55.275129439478206</v>
       </c>
     </row>
     <row r="68" spans="1:40">
@@ -9111,13 +9141,13 @@
         <v>106</v>
       </c>
       <c r="B68">
-        <v>97.22557297949336</v>
+        <v>97.225572979493364</v>
       </c>
       <c r="C68">
         <v>3505</v>
       </c>
       <c r="D68">
-        <v>18.15</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E68">
         <v>2.75</v>
@@ -9135,13 +9165,13 @@
         <v>18.73400001525879</v>
       </c>
       <c r="J68">
-        <v>19.75974998474121</v>
+        <v>19.759749984741209</v>
       </c>
       <c r="K68">
-        <v>17.56809984207153</v>
+        <v>17.568099842071529</v>
       </c>
       <c r="L68">
-        <v>12.02584995269775</v>
+        <v>12.025849952697749</v>
       </c>
       <c r="M68">
         <v>0.95</v>
@@ -9180,7 +9210,7 @@
         <v>21.74</v>
       </c>
       <c r="Z68">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AA68">
         <v>12.19</v>
@@ -9189,7 +9219,7 @@
         <v>172.46</v>
       </c>
       <c r="AC68">
-        <v>320.47</v>
+        <v>320.47000000000003</v>
       </c>
       <c r="AD68">
         <v>2</v>
@@ -9222,7 +9252,7 @@
         <v>100</v>
       </c>
       <c r="AN68">
-        <v>54.4975095700339</v>
+        <v>54.497509570033898</v>
       </c>
     </row>
     <row r="69" spans="1:40">
@@ -9230,43 +9260,43 @@
         <v>107</v>
       </c>
       <c r="B69">
-        <v>99.77382388419784</v>
+        <v>99.773823884197839</v>
       </c>
       <c r="C69">
         <v>2988</v>
       </c>
       <c r="D69">
-        <v>85.26000000000001</v>
+        <v>85.26</v>
       </c>
       <c r="E69">
         <v>5.86</v>
       </c>
       <c r="F69">
-        <v>0.4798590448765678</v>
+        <v>0.47985904487656778</v>
       </c>
       <c r="G69">
-        <v>8.369999999999999</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="H69">
-        <v>1.479910620622689</v>
+        <v>1.4799106206226891</v>
       </c>
       <c r="I69">
-        <v>87.68800048828125</v>
+        <v>87.688000488281247</v>
       </c>
       <c r="J69">
-        <v>91.20849990844727</v>
+        <v>91.208499908447266</v>
       </c>
       <c r="K69">
-        <v>78.35459983825683</v>
+        <v>78.354599838256831</v>
       </c>
       <c r="L69">
-        <v>48.78795003890991</v>
+        <v>48.787950038909912</v>
       </c>
       <c r="M69">
         <v>0.96</v>
       </c>
       <c r="N69">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -9293,7 +9323,7 @@
         <v>1</v>
       </c>
       <c r="X69">
-        <v>8.529999999999999</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="Y69">
         <v>108.5</v>
@@ -9311,13 +9341,13 @@
         <v>103.31</v>
       </c>
       <c r="AD69">
-        <v>35.12</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="AE69">
         <v>-92.16</v>
       </c>
       <c r="AF69">
-        <v>-81.79000000000001</v>
+        <v>-81.790000000000006</v>
       </c>
       <c r="AG69">
         <v>9233.33</v>
@@ -9338,10 +9368,10 @@
         <v>1</v>
       </c>
       <c r="AM69">
-        <v>-67.20999999999999</v>
+        <v>-67.209999999999994</v>
       </c>
       <c r="AN69">
-        <v>54.29506055362907</v>
+        <v>54.295060553629071</v>
       </c>
     </row>
     <row r="70" spans="1:40">
@@ -9349,7 +9379,7 @@
         <v>108</v>
       </c>
       <c r="B70">
-        <v>90.37997587454765</v>
+        <v>90.379975874547654</v>
       </c>
       <c r="C70">
         <v>3580</v>
@@ -9367,22 +9397,22 @@
         <v>3.28</v>
       </c>
       <c r="H70">
-        <v>-0.0909194912265341</v>
+        <v>-9.0919491226534102E-2</v>
       </c>
       <c r="I70">
-        <v>7.659999942779541</v>
+        <v>7.6599999427795407</v>
       </c>
       <c r="J70">
-        <v>6.705499935150146</v>
+        <v>6.7054999351501463</v>
       </c>
       <c r="K70">
-        <v>6.08920000076294</v>
+        <v>6.0892000007629399</v>
       </c>
       <c r="L70">
-        <v>5.319425008296967</v>
+        <v>5.3194250082969674</v>
       </c>
       <c r="M70">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N70">
         <v>1.26</v>
@@ -9412,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="X70">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Y70">
         <v>8</v>
@@ -9424,7 +9454,7 @@
         <v>6.03</v>
       </c>
       <c r="AB70">
-        <v>95.68000000000001</v>
+        <v>95.68</v>
       </c>
       <c r="AC70">
         <v>2834.48</v>
@@ -9460,7 +9490,7 @@
         <v>75</v>
       </c>
       <c r="AN70">
-        <v>53.48324852092132</v>
+        <v>53.483248520921322</v>
       </c>
     </row>
     <row r="71" spans="1:40">
@@ -9468,7 +9498,7 @@
         <v>109</v>
       </c>
       <c r="B71">
-        <v>92.85283474065139</v>
+        <v>92.852834740651389</v>
       </c>
       <c r="C71">
         <v>947</v>
@@ -9480,22 +9510,22 @@
         <v>2.15</v>
       </c>
       <c r="F71">
-        <v>-0.2173140856028563</v>
+        <v>-0.21731408560285631</v>
       </c>
       <c r="G71">
         <v>2.59</v>
       </c>
       <c r="H71">
-        <v>-0.3038610977444052</v>
+        <v>-0.30386109774440517</v>
       </c>
       <c r="I71">
-        <v>26.2560001373291</v>
+        <v>26.256000137329099</v>
       </c>
       <c r="J71">
-        <v>24.80299997329712</v>
+        <v>24.802999973297119</v>
       </c>
       <c r="K71">
-        <v>22.58760009765625</v>
+        <v>22.587600097656249</v>
       </c>
       <c r="L71">
         <v>16.93190000534058</v>
@@ -9504,7 +9534,7 @@
         <v>1.06</v>
       </c>
       <c r="N71">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -9543,7 +9573,7 @@
         <v>-1.04</v>
       </c>
       <c r="AB71">
-        <v>134.64</v>
+        <v>134.63999999999999</v>
       </c>
       <c r="AC71">
         <v>77.17</v>
@@ -9579,7 +9609,7 @@
         <v>218.52</v>
       </c>
       <c r="AN71">
-        <v>52.87869927405534</v>
+        <v>52.878699274055343</v>
       </c>
     </row>
     <row r="72" spans="1:40">
@@ -9587,37 +9617,37 @@
         <v>110</v>
       </c>
       <c r="B72">
-        <v>98.50723763570566</v>
+        <v>98.507237635705664</v>
       </c>
       <c r="C72">
         <v>2945</v>
       </c>
       <c r="D72">
-        <v>155.67</v>
+        <v>155.66999999999999</v>
       </c>
       <c r="E72">
         <v>3.04</v>
       </c>
       <c r="F72">
-        <v>-0.05006770120213189</v>
+        <v>-5.0067701202131887E-2</v>
       </c>
       <c r="G72">
         <v>3.39</v>
       </c>
       <c r="H72">
-        <v>-0.05697227859325021</v>
+        <v>-5.6972278593250207E-2</v>
       </c>
       <c r="I72">
-        <v>150.8660034179688</v>
+        <v>150.86600341796881</v>
       </c>
       <c r="J72">
         <v>144.5515007019043</v>
       </c>
       <c r="K72">
-        <v>146.5723999023438</v>
+        <v>146.57239990234379</v>
       </c>
       <c r="L72">
-        <v>94.39669853210449</v>
+        <v>94.396698532104494</v>
       </c>
       <c r="M72">
         <v>1.04</v>
@@ -9692,13 +9722,13 @@
         <v>4.79</v>
       </c>
       <c r="AL72">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AM72">
         <v>5.64</v>
       </c>
       <c r="AN72">
-        <v>51.62362171708143</v>
+        <v>51.623621717081427</v>
       </c>
     </row>
     <row r="73" spans="1:40">
@@ -9706,7 +9736,7 @@
         <v>111</v>
       </c>
       <c r="B73">
-        <v>96.07961399276238</v>
+        <v>96.079613992762376</v>
       </c>
       <c r="C73">
         <v>448</v>
@@ -9718,19 +9748,19 @@
         <v>6</v>
       </c>
       <c r="F73">
-        <v>0.5061674648946592</v>
+        <v>0.50616746489465925</v>
       </c>
       <c r="G73">
         <v>6.6</v>
       </c>
       <c r="H73">
-        <v>0.9336691082507586</v>
+        <v>0.93366910825075855</v>
       </c>
       <c r="I73">
-        <v>5.303999996185302</v>
+        <v>5.3039999961853024</v>
       </c>
       <c r="J73">
-        <v>4.341499960422516</v>
+        <v>4.3414999604225164</v>
       </c>
       <c r="K73">
         <v>3.959799990653992</v>
@@ -9808,7 +9838,7 @@
         <v>233</v>
       </c>
       <c r="AK73">
-        <v>-2.22</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="AL73">
         <v>-0.01</v>
@@ -9817,7 +9847,7 @@
         <v>99.55</v>
       </c>
       <c r="AN73">
-        <v>51.35349862921166</v>
+        <v>51.353498629211657</v>
       </c>
     </row>
     <row r="74" spans="1:40">
@@ -9834,25 +9864,25 @@
         <v>37.64</v>
       </c>
       <c r="E74">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F74">
-        <v>-0.1966431841600701</v>
+        <v>-0.19664318416007009</v>
       </c>
       <c r="G74">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H74">
-        <v>-0.3470666410958572</v>
+        <v>-0.34706664109585722</v>
       </c>
       <c r="I74">
-        <v>37.55999984741211</v>
+        <v>37.559999847412108</v>
       </c>
       <c r="J74">
-        <v>36.80750026702881</v>
+        <v>36.807500267028807</v>
       </c>
       <c r="K74">
-        <v>36.91540016174316</v>
+        <v>36.915400161743158</v>
       </c>
       <c r="L74">
         <v>31.67000003814697</v>
@@ -9891,7 +9921,7 @@
         <v>16.89</v>
       </c>
       <c r="Y74">
-        <v>40.34</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="Z74">
         <v>6.97</v>
@@ -9909,7 +9939,7 @@
         <v>17.52</v>
       </c>
       <c r="AE74">
-        <v>79.90000000000001</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="AF74">
         <v>246.26</v>
@@ -9936,7 +9966,7 @@
         <v>-23.99</v>
       </c>
       <c r="AN74">
-        <v>51.1142902843652</v>
+        <v>51.114290284365197</v>
       </c>
     </row>
     <row r="75" spans="1:40">
@@ -9944,7 +9974,7 @@
         <v>113</v>
       </c>
       <c r="B75">
-        <v>99.33655006031363</v>
+        <v>99.336550060313627</v>
       </c>
       <c r="C75">
         <v>1149</v>
@@ -9962,22 +9992,22 @@
         <v>4.32</v>
       </c>
       <c r="H75">
-        <v>0.2300359736699674</v>
+        <v>0.23003597366996739</v>
       </c>
       <c r="I75">
         <v>22.54200019836426</v>
       </c>
       <c r="J75">
-        <v>19.38049974441528</v>
+        <v>19.380499744415278</v>
       </c>
       <c r="K75">
-        <v>17.29119987487793</v>
+        <v>17.291199874877929</v>
       </c>
       <c r="L75">
         <v>11.30721101760864</v>
       </c>
       <c r="M75">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N75">
         <v>1.3</v>
@@ -10016,7 +10046,7 @@
         <v>5.5</v>
       </c>
       <c r="AA75">
-        <v>36.12</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="AB75">
         <v>111.4</v>
@@ -10025,7 +10055,7 @@
         <v>244.88</v>
       </c>
       <c r="AD75">
-        <v>20.06</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="AE75">
         <v>-34.54</v>
@@ -10055,7 +10085,7 @@
         <v>46.74</v>
       </c>
       <c r="AN75">
-        <v>50.20091938376159</v>
+        <v>50.200919383761587</v>
       </c>
     </row>
     <row r="76" spans="1:40">
@@ -10063,7 +10093,7 @@
         <v>114</v>
       </c>
       <c r="B76">
-        <v>95.09951749095296</v>
+        <v>95.099517490952962</v>
       </c>
       <c r="C76">
         <v>1546</v>
@@ -10075,25 +10105,25 @@
         <v>1.85</v>
       </c>
       <c r="F76">
-        <v>-0.2736892713559094</v>
+        <v>-0.27368927135590942</v>
       </c>
       <c r="G76">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H76">
-        <v>-0.3162055387019629</v>
+        <v>-0.31620553870196288</v>
       </c>
       <c r="I76">
-        <v>16.7180004119873</v>
+        <v>16.718000411987301</v>
       </c>
       <c r="J76">
-        <v>17.53625001907348</v>
+        <v>17.536250019073481</v>
       </c>
       <c r="K76">
         <v>16.53749994277954</v>
       </c>
       <c r="L76">
-        <v>11.67192497968674</v>
+        <v>11.671924979686739</v>
       </c>
       <c r="M76">
         <v>0.95</v>
@@ -10174,7 +10204,7 @@
         <v>560</v>
       </c>
       <c r="AN76">
-        <v>48.87498170631545</v>
+        <v>48.874981706315452</v>
       </c>
     </row>
     <row r="77" spans="1:40">
@@ -10182,43 +10212,43 @@
         <v>115</v>
       </c>
       <c r="B77">
-        <v>99.96984318455972</v>
+        <v>99.969843184559721</v>
       </c>
       <c r="C77">
         <v>1751</v>
       </c>
       <c r="D77">
-        <v>96.56999999999999</v>
+        <v>96.57</v>
       </c>
       <c r="E77">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="F77">
-        <v>0.1735538689516457</v>
+        <v>0.17355386895164571</v>
       </c>
       <c r="G77">
         <v>7.6</v>
       </c>
       <c r="H77">
-        <v>1.242280132189702</v>
+        <v>1.2422801321897019</v>
       </c>
       <c r="I77">
-        <v>88.3979995727539</v>
+        <v>88.397999572753903</v>
       </c>
       <c r="J77">
-        <v>79.45150032043458</v>
+        <v>79.451500320434576</v>
       </c>
       <c r="K77">
-        <v>77.27139991760254</v>
+        <v>77.271399917602537</v>
       </c>
       <c r="L77">
         <v>41.519524974823</v>
       </c>
       <c r="M77">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N77">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P77">
         <v>0</v>
@@ -10233,7 +10263,7 @@
         <v>1</v>
       </c>
       <c r="T77">
-        <v>6.111111111111111</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="U77" t="b">
         <v>0</v>
@@ -10257,22 +10287,22 @@
         <v>155</v>
       </c>
       <c r="AB77">
-        <v>93.73999999999999</v>
+        <v>93.74</v>
       </c>
       <c r="AC77">
-        <v>81.29000000000001</v>
+        <v>81.290000000000006</v>
       </c>
       <c r="AD77">
         <v>-36.4</v>
       </c>
       <c r="AE77">
-        <v>71.81999999999999</v>
+        <v>71.819999999999993</v>
       </c>
       <c r="AF77">
         <v>-41.03</v>
       </c>
       <c r="AG77">
-        <v>-9.859999999999999</v>
+        <v>-9.86</v>
       </c>
       <c r="AH77" t="s">
         <v>170</v>
@@ -10293,7 +10323,7 @@
         <v>115.86</v>
       </c>
       <c r="AN77">
-        <v>47.68227384461942</v>
+        <v>47.682273844619417</v>
       </c>
     </row>
     <row r="78" spans="1:40">
@@ -10301,7 +10331,7 @@
         <v>116</v>
       </c>
       <c r="B78">
-        <v>90.95295536791315</v>
+        <v>90.952955367913148</v>
       </c>
       <c r="C78">
         <v>2878</v>
@@ -10313,25 +10343,25 @@
         <v>2.1</v>
       </c>
       <c r="F78">
-        <v>-0.2267099498950318</v>
+        <v>-0.22670994989503179</v>
       </c>
       <c r="G78">
         <v>1.82</v>
       </c>
       <c r="H78">
-        <v>-0.5414915861773917</v>
+        <v>-0.54149158617739168</v>
       </c>
       <c r="I78">
-        <v>28.64799957275391</v>
+        <v>28.647999572753911</v>
       </c>
       <c r="J78">
-        <v>28.79349985122681</v>
+        <v>28.793499851226809</v>
       </c>
       <c r="K78">
         <v>28.36999984741211</v>
       </c>
       <c r="L78">
-        <v>25.38699996948242</v>
+        <v>25.386999969482421</v>
       </c>
       <c r="M78">
         <v>0.99</v>
@@ -10352,7 +10382,7 @@
         <v>0</v>
       </c>
       <c r="T78">
-        <v>3.888888888888889</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="U78" t="b">
         <v>0</v>
@@ -10420,7 +10450,7 @@
         <v>117</v>
       </c>
       <c r="B79">
-        <v>95.37092882991556</v>
+        <v>95.370928829915556</v>
       </c>
       <c r="C79">
         <v>1780</v>
@@ -10432,25 +10462,25 @@
         <v>1.56</v>
       </c>
       <c r="F79">
-        <v>-0.3281852842505275</v>
+        <v>-0.32818528425052751</v>
       </c>
       <c r="G79">
         <v>2.52</v>
       </c>
       <c r="H79">
-        <v>-0.3254638694201312</v>
+        <v>-0.32546386942013122</v>
       </c>
       <c r="I79">
-        <v>52.33399963378906</v>
+        <v>52.333999633789062</v>
       </c>
       <c r="J79">
-        <v>53.24949970245361</v>
+        <v>53.249499702453612</v>
       </c>
       <c r="K79">
-        <v>51.55859992980957</v>
+        <v>51.558599929809567</v>
       </c>
       <c r="L79">
-        <v>39.37059987068177</v>
+        <v>39.370599870681772</v>
       </c>
       <c r="M79">
         <v>0.98</v>
@@ -10510,7 +10540,7 @@
         <v>76.47</v>
       </c>
       <c r="AG79">
-        <v>-83.95999999999999</v>
+        <v>-83.96</v>
       </c>
       <c r="AH79" t="s">
         <v>175</v>
@@ -10531,7 +10561,7 @@
         <v>257.89</v>
       </c>
       <c r="AN79">
-        <v>47.38486741555749</v>
+        <v>47.384867415557487</v>
       </c>
     </row>
     <row r="80" spans="1:40">
@@ -10539,7 +10569,7 @@
         <v>118</v>
       </c>
       <c r="B80">
-        <v>91.91797346200241</v>
+        <v>91.917973462002408</v>
       </c>
       <c r="C80">
         <v>650</v>
@@ -10557,7 +10587,7 @@
         <v>9.85</v>
       </c>
       <c r="H80">
-        <v>1.936654936052325</v>
+        <v>1.9366549360523251</v>
       </c>
       <c r="I80">
         <v>14.94999980926514</v>
@@ -10566,13 +10596,13 @@
         <v>13.05149989128113</v>
       </c>
       <c r="K80">
-        <v>8.666099967956542</v>
+        <v>8.6660999679565425</v>
       </c>
       <c r="L80">
         <v>5.566874989271164</v>
       </c>
       <c r="M80">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N80">
         <v>1.73</v>
@@ -10590,7 +10620,7 @@
         <v>5</v>
       </c>
       <c r="T80">
-        <v>8.333333333333332</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="U80" t="b">
         <v>0</v>
@@ -10605,7 +10635,7 @@
         <v>3.28</v>
       </c>
       <c r="Y80">
-        <v>16.35</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="Z80">
         <v>1.72</v>
@@ -10614,13 +10644,13 @@
         <v>-27.73</v>
       </c>
       <c r="AB80">
-        <v>76.56999999999999</v>
+        <v>76.569999999999993</v>
       </c>
       <c r="AC80">
         <v>51.48</v>
       </c>
       <c r="AD80">
-        <v>-9.359999999999999</v>
+        <v>-9.36</v>
       </c>
       <c r="AE80">
         <v>0</v>
@@ -10650,7 +10680,7 @@
         <v>104.76</v>
       </c>
       <c r="AN80">
-        <v>45.48903620756595</v>
+        <v>45.489036207565952</v>
       </c>
     </row>
     <row r="81" spans="1:40">
@@ -10658,7 +10688,7 @@
         <v>119</v>
       </c>
       <c r="B81">
-        <v>91.57117008443907</v>
+        <v>91.571170084439075</v>
       </c>
       <c r="C81">
         <v>2517</v>
@@ -10670,25 +10700,25 @@
         <v>1.87</v>
       </c>
       <c r="F81">
-        <v>-0.2699309256390391</v>
+        <v>-0.26993092563903909</v>
       </c>
       <c r="G81">
         <v>2.67</v>
       </c>
       <c r="H81">
-        <v>-0.2791722158292896</v>
+        <v>-0.27917221582928958</v>
       </c>
       <c r="I81">
-        <v>63.27599868774414</v>
+        <v>63.275998687744142</v>
       </c>
       <c r="J81">
-        <v>65.74449939727783</v>
+        <v>65.744499397277835</v>
       </c>
       <c r="K81">
         <v>61.37999961853027</v>
       </c>
       <c r="L81">
-        <v>44.23094996452332</v>
+        <v>44.230949964523319</v>
       </c>
       <c r="M81">
         <v>0.96</v>
@@ -10709,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="T81">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U81" t="b">
         <v>0</v>
@@ -10727,7 +10757,7 @@
         <v>71.34</v>
       </c>
       <c r="Z81">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AA81">
         <v>1.52</v>
@@ -10760,16 +10790,16 @@
         <v>207</v>
       </c>
       <c r="AK81">
-        <v>-0.29</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="AL81">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="AM81">
         <v>424.14</v>
       </c>
       <c r="AN81">
-        <v>43.17016034977697</v>
+        <v>43.170160349776971</v>
       </c>
     </row>
     <row r="82" spans="1:40">
@@ -10777,7 +10807,7 @@
         <v>120</v>
       </c>
       <c r="B82">
-        <v>91.99336550060315</v>
+        <v>91.993365500603147</v>
       </c>
       <c r="C82">
         <v>5977</v>
@@ -10789,31 +10819,31 @@
         <v>2.91</v>
       </c>
       <c r="F82">
-        <v>-0.07449694836178823</v>
+        <v>-7.4496948361788232E-2</v>
       </c>
       <c r="G82">
         <v>2.96</v>
       </c>
       <c r="H82">
-        <v>-0.189675018886996</v>
+        <v>-0.18967501888699601</v>
       </c>
       <c r="I82">
-        <v>32.29399909973144</v>
+        <v>32.293999099731437</v>
       </c>
       <c r="J82">
         <v>28.96859979629517</v>
       </c>
       <c r="K82">
-        <v>28.69535995483399</v>
+        <v>28.695359954833989</v>
       </c>
       <c r="L82">
         <v>25.69777495384216</v>
       </c>
       <c r="M82">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N82">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -10858,7 +10888,7 @@
         <v>120.36</v>
       </c>
       <c r="AD82">
-        <v>-8.050000000000001</v>
+        <v>-8.0500000000000007</v>
       </c>
       <c r="AE82">
         <v>122.89</v>
@@ -10888,7 +10918,7 @@
         <v>266.67</v>
       </c>
       <c r="AN82">
-        <v>43.13598691006685</v>
+        <v>43.135986910066848</v>
       </c>
     </row>
     <row r="83" spans="1:40">
@@ -10908,25 +10938,25 @@
         <v>4.82</v>
       </c>
       <c r="F83">
-        <v>0.2844250675993168</v>
+        <v>0.28442506759931679</v>
       </c>
       <c r="G83">
         <v>4.41</v>
       </c>
       <c r="H83">
-        <v>0.2578109658244722</v>
+        <v>0.25781096582447222</v>
       </c>
       <c r="I83">
-        <v>14.98400020599365</v>
+        <v>14.984000205993651</v>
       </c>
       <c r="J83">
         <v>14.20149998664856</v>
       </c>
       <c r="K83">
-        <v>11.96290006637573</v>
+        <v>11.962900066375729</v>
       </c>
       <c r="L83">
-        <v>10.07727503538132</v>
+        <v>10.077275035381319</v>
       </c>
       <c r="M83">
         <v>1.06</v>
@@ -10971,7 +11001,7 @@
         <v>-48.07</v>
       </c>
       <c r="AB83">
-        <v>64.31999999999999</v>
+        <v>64.319999999999993</v>
       </c>
       <c r="AC83">
         <v>53.92</v>
@@ -11015,7 +11045,7 @@
         <v>122</v>
       </c>
       <c r="B84">
-        <v>94.75271411338963</v>
+        <v>94.752714113389629</v>
       </c>
       <c r="C84">
         <v>2870</v>
@@ -11027,31 +11057,31 @@
         <v>2.09</v>
       </c>
       <c r="F84">
-        <v>-0.2285891227534669</v>
+        <v>-0.22858912275346691</v>
       </c>
       <c r="G84">
         <v>3.63</v>
       </c>
       <c r="H84">
-        <v>0.01709436715209618</v>
+        <v>1.7094367152096179E-2</v>
       </c>
       <c r="I84">
-        <v>25.67400016784668</v>
+        <v>25.674000167846678</v>
       </c>
       <c r="J84">
         <v>25.82200012207031</v>
       </c>
       <c r="K84">
-        <v>23.15520015716553</v>
+        <v>23.155200157165531</v>
       </c>
       <c r="L84">
-        <v>17.80660001277923</v>
+        <v>17.806600012779231</v>
       </c>
       <c r="M84">
         <v>0.99</v>
       </c>
       <c r="N84">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -11066,7 +11096,7 @@
         <v>9</v>
       </c>
       <c r="T84">
-        <v>17.22222222222222</v>
+        <v>17.222222222222221</v>
       </c>
       <c r="U84" t="b">
         <v>1</v>
@@ -11096,7 +11126,7 @@
         <v>248.36</v>
       </c>
       <c r="AD84">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="AE84">
         <v>288.89</v>
@@ -11126,7 +11156,7 @@
         <v>24</v>
       </c>
       <c r="AN84">
-        <v>41.88764884442286</v>
+        <v>41.887648844422863</v>
       </c>
     </row>
     <row r="85" spans="1:40">
@@ -11134,13 +11164,13 @@
         <v>123</v>
       </c>
       <c r="B85">
-        <v>98.43184559710495</v>
+        <v>98.431845597104953</v>
       </c>
       <c r="C85">
         <v>1715</v>
       </c>
       <c r="D85">
-        <v>139.52</v>
+        <v>139.52000000000001</v>
       </c>
       <c r="E85">
         <v>2.5</v>
@@ -11149,13 +11179,13 @@
         <v>-0.1515430355576276</v>
       </c>
       <c r="G85">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H85">
         <v>-0.3223777591807418</v>
       </c>
       <c r="I85">
-        <v>139.1880004882813</v>
+        <v>139.18800048828129</v>
       </c>
       <c r="J85">
         <v>133.5630001068115</v>
@@ -11170,7 +11200,7 @@
         <v>1.04</v>
       </c>
       <c r="N85">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -11245,7 +11275,7 @@
         <v>52.33</v>
       </c>
       <c r="AN85">
-        <v>41.71283693784734</v>
+        <v>41.712836937847342</v>
       </c>
     </row>
     <row r="86" spans="1:40">
@@ -11253,7 +11283,7 @@
         <v>124</v>
       </c>
       <c r="B86">
-        <v>93.22979493365501</v>
+        <v>93.229794933655015</v>
       </c>
       <c r="C86">
         <v>1961</v>
@@ -11265,16 +11295,16 @@
         <v>1.28</v>
       </c>
       <c r="F86">
-        <v>-0.3808021242867105</v>
+        <v>-0.38080212428671051</v>
       </c>
       <c r="G86">
         <v>5.38</v>
       </c>
       <c r="H86">
-        <v>0.5571636590452475</v>
+        <v>0.55716365904524745</v>
       </c>
       <c r="I86">
-        <v>107.2579986572266</v>
+        <v>107.25799865722659</v>
       </c>
       <c r="J86">
         <v>106.2805004119873</v>
@@ -11283,7 +11313,7 @@
         <v>103.6112004089355</v>
       </c>
       <c r="L86">
-        <v>80.13219980239869</v>
+        <v>80.132199802398688</v>
       </c>
       <c r="M86">
         <v>1.01</v>
@@ -11340,7 +11370,7 @@
         <v>-35.81</v>
       </c>
       <c r="AF86">
-        <v>-9.199999999999999</v>
+        <v>-9.1999999999999993</v>
       </c>
       <c r="AG86">
         <v>3.82</v>
@@ -11364,7 +11394,7 @@
         <v>31.52</v>
       </c>
       <c r="AN86">
-        <v>41.67965710252997</v>
+        <v>41.679657102529973</v>
       </c>
     </row>
     <row r="87" spans="1:40">
@@ -11372,7 +11402,7 @@
         <v>125</v>
       </c>
       <c r="B87">
-        <v>94.91857659831122</v>
+        <v>94.918576598311219</v>
       </c>
       <c r="C87">
         <v>817</v>
@@ -11381,28 +11411,28 @@
         <v>4.96</v>
       </c>
       <c r="E87">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F87">
-        <v>-0.410868890021672</v>
+        <v>-0.41086889002167198</v>
       </c>
       <c r="G87">
         <v>1.51</v>
       </c>
       <c r="H87">
-        <v>-0.6371610035984641</v>
+        <v>-0.63716100359846406</v>
       </c>
       <c r="I87">
-        <v>4.898000049591064</v>
+        <v>4.8980000495910643</v>
       </c>
       <c r="J87">
-        <v>4.850499963760376</v>
+        <v>4.8504999637603756</v>
       </c>
       <c r="K87">
-        <v>4.779400005340576</v>
+        <v>4.7794000053405759</v>
       </c>
       <c r="L87">
-        <v>4.269449995160103</v>
+        <v>4.2694499951601026</v>
       </c>
       <c r="M87">
         <v>1.01</v>
@@ -11447,10 +11477,10 @@
         <v>155</v>
       </c>
       <c r="AB87">
-        <v>78.23999999999999</v>
+        <v>78.239999999999995</v>
       </c>
       <c r="AC87">
-        <v>18.92</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="AD87">
         <v>-54.93</v>
@@ -11483,7 +11513,7 @@
         <v>102.44</v>
       </c>
       <c r="AN87">
-        <v>41.39252664333515</v>
+        <v>41.392526643335152</v>
       </c>
     </row>
     <row r="88" spans="1:40">
@@ -11491,7 +11521,7 @@
         <v>126</v>
       </c>
       <c r="B88">
-        <v>97.2708082026538</v>
+        <v>97.270808202653797</v>
       </c>
       <c r="C88">
         <v>1906</v>
@@ -11515,13 +11545,13 @@
         <v>37.64399948120117</v>
       </c>
       <c r="J88">
-        <v>38.07700004577637</v>
+        <v>38.077000045776373</v>
       </c>
       <c r="K88">
-        <v>35.64350009918213</v>
+        <v>35.643500099182127</v>
       </c>
       <c r="L88">
-        <v>25.53326549530029</v>
+        <v>25.533265495300292</v>
       </c>
       <c r="M88">
         <v>0.99</v>
@@ -11602,7 +11632,7 @@
         <v>17.95</v>
       </c>
       <c r="AN88">
-        <v>41.22327874577032</v>
+        <v>41.223278745770322</v>
       </c>
     </row>
     <row r="89" spans="1:40">
@@ -11610,7 +11640,7 @@
         <v>127</v>
       </c>
       <c r="B89">
-        <v>93.59167671893847</v>
+        <v>93.591676718938473</v>
       </c>
       <c r="C89">
         <v>725</v>
@@ -11622,7 +11652,7 @@
         <v>2.91</v>
       </c>
       <c r="F89">
-        <v>-0.07449694836178823</v>
+        <v>-7.4496948361788232E-2</v>
       </c>
       <c r="G89">
         <v>4.37</v>
@@ -11631,22 +11661,22 @@
         <v>0.2454665248669145</v>
       </c>
       <c r="I89">
-        <v>56.83399963378906</v>
+        <v>56.833999633789062</v>
       </c>
       <c r="J89">
-        <v>54.00500011444092</v>
+        <v>54.005000114440918</v>
       </c>
       <c r="K89">
-        <v>49.46120018005371</v>
+        <v>49.461200180053709</v>
       </c>
       <c r="L89">
-        <v>38.30500001907349</v>
+        <v>38.305000019073489</v>
       </c>
       <c r="M89">
         <v>1.05</v>
       </c>
       <c r="N89">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P89">
         <v>0</v>
@@ -11721,7 +11751,7 @@
         <v>80</v>
       </c>
       <c r="AN89">
-        <v>39.5030784207575</v>
+        <v>39.503078420757497</v>
       </c>
     </row>
     <row r="90" spans="1:40">
@@ -11741,25 +11771,25 @@
         <v>2.14</v>
       </c>
       <c r="F90">
-        <v>-0.2191932584612913</v>
+        <v>-0.21919325846129131</v>
       </c>
       <c r="G90">
         <v>2.74</v>
       </c>
       <c r="H90">
-        <v>-0.2575694441535635</v>
+        <v>-0.25756944415356348</v>
       </c>
       <c r="I90">
-        <v>181.0760040283203</v>
+        <v>181.07600402832031</v>
       </c>
       <c r="J90">
         <v>175.1340026855469</v>
       </c>
       <c r="K90">
-        <v>177.4292013549805</v>
+        <v>177.42920135498051</v>
       </c>
       <c r="L90">
-        <v>134.1933876037598</v>
+        <v>134.19338760375979</v>
       </c>
       <c r="M90">
         <v>1.03</v>
@@ -11807,7 +11837,7 @@
         <v>47.28</v>
       </c>
       <c r="AC90">
-        <v>90.31999999999999</v>
+        <v>90.32</v>
       </c>
       <c r="AD90">
         <v>14.69</v>
@@ -11840,7 +11870,7 @@
         <v>74.39</v>
       </c>
       <c r="AN90">
-        <v>39.49442548421081</v>
+        <v>39.494425484210808</v>
       </c>
     </row>
     <row r="91" spans="1:40">
@@ -11848,7 +11878,7 @@
         <v>129</v>
       </c>
       <c r="B91">
-        <v>92.03860072376358</v>
+        <v>92.038600723763579</v>
       </c>
       <c r="C91">
         <v>1553</v>
@@ -11860,19 +11890,19 @@
         <v>2.38</v>
       </c>
       <c r="F91">
-        <v>-0.1740931098588488</v>
+        <v>-0.17409310985884879</v>
       </c>
       <c r="G91">
         <v>2.57</v>
       </c>
       <c r="H91">
-        <v>-0.310033318223184</v>
+        <v>-0.31003331822318397</v>
       </c>
       <c r="I91">
         <v>25.57200012207031</v>
       </c>
       <c r="J91">
-        <v>25.23300008773804</v>
+        <v>25.233000087738041</v>
       </c>
       <c r="K91">
         <v>24.21487155914307</v>
@@ -11917,13 +11947,13 @@
         <v>27.05</v>
       </c>
       <c r="Z91">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="AA91">
         <v>29.28</v>
       </c>
       <c r="AB91">
-        <v>68.73999999999999</v>
+        <v>68.739999999999995</v>
       </c>
       <c r="AC91">
         <v>12.89</v>
@@ -11959,7 +11989,7 @@
         <v>59.34</v>
       </c>
       <c r="AN91">
-        <v>39.43704317152176</v>
+        <v>39.437043171521758</v>
       </c>
     </row>
     <row r="92" spans="1:40">
@@ -11976,16 +12006,16 @@
         <v>16.46</v>
       </c>
       <c r="E92">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="F92">
-        <v>-0.1571805541329329</v>
+        <v>-0.15718055413293289</v>
       </c>
       <c r="G92">
         <v>3.26</v>
       </c>
       <c r="H92">
-        <v>-0.09709171170531299</v>
+        <v>-9.7091711705312986E-2</v>
       </c>
       <c r="I92">
         <v>16.6939998626709</v>
@@ -11994,10 +12024,10 @@
         <v>16.43949990272522</v>
       </c>
       <c r="K92">
-        <v>15.8093999671936</v>
+        <v>15.809399967193601</v>
       </c>
       <c r="L92">
-        <v>13.12554998397827</v>
+        <v>13.125549983978271</v>
       </c>
       <c r="M92">
         <v>1.02</v>
@@ -12030,25 +12060,25 @@
         <v>0</v>
       </c>
       <c r="X92">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="Y92">
         <v>18.38</v>
       </c>
       <c r="Z92">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="AA92">
         <v>1.08</v>
       </c>
       <c r="AB92">
-        <v>40.87</v>
+        <v>40.869999999999997</v>
       </c>
       <c r="AC92">
         <v>127.59</v>
       </c>
       <c r="AD92">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AE92">
         <v>500</v>
@@ -12057,7 +12087,7 @@
         <v>92.31</v>
       </c>
       <c r="AG92">
-        <v>-156.52</v>
+        <v>-156.52000000000001</v>
       </c>
       <c r="AH92" t="s">
         <v>166</v>
@@ -12075,10 +12105,10 @@
         <v>0.92</v>
       </c>
       <c r="AM92">
-        <v>607.6900000000001</v>
+        <v>607.69000000000005</v>
       </c>
       <c r="AN92">
-        <v>38.76274693938475</v>
+        <v>38.762746939384748</v>
       </c>
     </row>
     <row r="93" spans="1:40">
@@ -12086,13 +12116,13 @@
         <v>131</v>
       </c>
       <c r="B93">
-        <v>95.9891435464415</v>
+        <v>95.989143546441497</v>
       </c>
       <c r="C93">
         <v>2501</v>
       </c>
       <c r="D93">
-        <v>33.09</v>
+        <v>33.090000000000003</v>
       </c>
       <c r="E93">
         <v>3.99</v>
@@ -12107,16 +12137,16 @@
         <v>-0.1433833652961545</v>
       </c>
       <c r="I93">
-        <v>33.06399993896484</v>
+        <v>33.063999938964841</v>
       </c>
       <c r="J93">
-        <v>32.44143333435058</v>
+        <v>32.441433334350577</v>
       </c>
       <c r="K93">
-        <v>30.75146293640137</v>
+        <v>30.751462936401371</v>
       </c>
       <c r="L93">
-        <v>27.16253005981445</v>
+        <v>27.162530059814451</v>
       </c>
       <c r="M93">
         <v>1.02</v>
@@ -12197,7 +12227,7 @@
         <v>-55.3</v>
       </c>
       <c r="AN93">
-        <v>38.00746250202288</v>
+        <v>38.007462502022882</v>
       </c>
     </row>
     <row r="94" spans="1:40">
@@ -12205,7 +12235,7 @@
         <v>132</v>
       </c>
       <c r="B94">
-        <v>92.89806996381182</v>
+        <v>92.898069963811821</v>
       </c>
       <c r="C94">
         <v>1735</v>
@@ -12217,25 +12247,25 @@
         <v>1.85</v>
       </c>
       <c r="F94">
-        <v>-0.2736892713559094</v>
+        <v>-0.27368927135590942</v>
       </c>
       <c r="G94">
         <v>1.86</v>
       </c>
       <c r="H94">
-        <v>-0.5291471452198339</v>
+        <v>-0.52914714521983386</v>
       </c>
       <c r="I94">
         <v>36.27600021362305</v>
       </c>
       <c r="J94">
-        <v>36.07800045013428</v>
+        <v>36.078000450134283</v>
       </c>
       <c r="K94">
-        <v>35.34980407714843</v>
+        <v>35.349804077148427</v>
       </c>
       <c r="L94">
-        <v>28.15711511611939</v>
+        <v>28.157115116119389</v>
       </c>
       <c r="M94">
         <v>1.01</v>
@@ -12289,7 +12319,7 @@
         <v>14.12</v>
       </c>
       <c r="AE94">
-        <v>-8.449999999999999</v>
+        <v>-8.4499999999999993</v>
       </c>
       <c r="AF94">
         <v>20.34</v>
@@ -12307,7 +12337,7 @@
         <v>208</v>
       </c>
       <c r="AK94">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AL94">
         <v>3.1</v>
@@ -12316,7 +12346,7 @@
         <v>54.23</v>
       </c>
       <c r="AN94">
-        <v>37.67682519191389</v>
+        <v>37.676825191913892</v>
       </c>
     </row>
     <row r="95" spans="1:40">
@@ -12324,7 +12354,7 @@
         <v>133</v>
       </c>
       <c r="B95">
-        <v>91.07358262967431</v>
+        <v>91.073582629674306</v>
       </c>
       <c r="C95">
         <v>3</v>
@@ -12342,13 +12372,13 @@
         <v>32.81</v>
       </c>
       <c r="H95">
-        <v>9.022364045690471</v>
+        <v>9.0223640456904715</v>
       </c>
       <c r="I95">
-        <v>3.743999981880188</v>
+        <v>3.7439999818801879</v>
       </c>
       <c r="J95">
-        <v>2.012999999523163</v>
+        <v>2.0129999995231631</v>
       </c>
       <c r="K95">
         <v>1.7467999958992</v>
@@ -12387,7 +12417,7 @@
         <v>0</v>
       </c>
       <c r="X95">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Y95">
         <v>6.45</v>
@@ -12405,7 +12435,7 @@
         <v>43.31</v>
       </c>
       <c r="AD95">
-        <v>-71.01000000000001</v>
+        <v>-71.010000000000005</v>
       </c>
       <c r="AE95">
         <v>-100</v>
@@ -12443,7 +12473,7 @@
         <v>134</v>
       </c>
       <c r="B96">
-        <v>92.58142340168878</v>
+        <v>92.581423401688781</v>
       </c>
       <c r="C96">
         <v>1219</v>
@@ -12461,10 +12491,10 @@
         <v>3.55</v>
       </c>
       <c r="H96">
-        <v>-0.007594514763019331</v>
+        <v>-7.594514763019331E-3</v>
       </c>
       <c r="I96">
-        <v>16.61599998474121</v>
+        <v>16.615999984741212</v>
       </c>
       <c r="J96">
         <v>16.59899988174438</v>
@@ -12473,7 +12503,7 @@
         <v>15.84039991378784</v>
       </c>
       <c r="L96">
-        <v>11.41279999256134</v>
+        <v>11.412799992561339</v>
       </c>
       <c r="M96">
         <v>1</v>
@@ -12524,7 +12554,7 @@
         <v>176.47</v>
       </c>
       <c r="AD96">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="AE96">
         <v>0</v>
@@ -12554,7 +12584,7 @@
         <v>82.61</v>
       </c>
       <c r="AN96">
-        <v>35.7954664939347</v>
+        <v>35.795466493934697</v>
       </c>
     </row>
     <row r="97" spans="1:40">
@@ -12562,7 +12592,7 @@
         <v>135</v>
       </c>
       <c r="B97">
-        <v>91.61640530759951</v>
+        <v>91.616405307599507</v>
       </c>
       <c r="C97">
         <v>2358</v>
@@ -12574,25 +12604,25 @@
         <v>1.53</v>
       </c>
       <c r="F97">
-        <v>-0.3338228028258328</v>
+        <v>-0.33382280282583282</v>
       </c>
       <c r="G97">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H97">
-        <v>-0.4643388301926558</v>
+        <v>-0.46433883019265582</v>
       </c>
       <c r="I97">
-        <v>55.31800003051758</v>
+        <v>55.318000030517581</v>
       </c>
       <c r="J97">
         <v>56.4375</v>
       </c>
       <c r="K97">
-        <v>56.11859977722168</v>
+        <v>56.118599777221682</v>
       </c>
       <c r="L97">
-        <v>43.87829995155334</v>
+        <v>43.878299951553338</v>
       </c>
       <c r="M97">
         <v>0.98</v>
@@ -12652,7 +12682,7 @@
         <v>174.42</v>
       </c>
       <c r="AG97">
-        <v>290.91</v>
+        <v>290.91000000000003</v>
       </c>
       <c r="AH97" t="s">
         <v>175</v>
@@ -12673,7 +12703,7 @@
         <v>3.97</v>
       </c>
       <c r="AN97">
-        <v>35.75637086875627</v>
+        <v>35.756370868756271</v>
       </c>
     </row>
     <row r="98" spans="1:40">
@@ -12681,7 +12711,7 @@
         <v>136</v>
       </c>
       <c r="B98">
-        <v>93.16948130277443</v>
+        <v>93.169481302774429</v>
       </c>
       <c r="C98">
         <v>1603</v>
@@ -12690,28 +12720,28 @@
         <v>56.49</v>
       </c>
       <c r="E98">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="F98">
-        <v>-0.1571805541329329</v>
+        <v>-0.15718055413293289</v>
       </c>
       <c r="G98">
         <v>2.76</v>
       </c>
       <c r="H98">
-        <v>-0.2513972236747848</v>
+        <v>-0.25139722367478479</v>
       </c>
       <c r="I98">
-        <v>55.71000061035156</v>
+        <v>55.710000610351557</v>
       </c>
       <c r="J98">
-        <v>55.57649993896484</v>
+        <v>55.576499938964837</v>
       </c>
       <c r="K98">
-        <v>53.18540008544922</v>
+        <v>53.185400085449217</v>
       </c>
       <c r="L98">
-        <v>47.68795009613037</v>
+        <v>47.687950096130372</v>
       </c>
       <c r="M98">
         <v>1</v>
@@ -12762,10 +12792,10 @@
         <v>102.35</v>
       </c>
       <c r="AD98">
-        <v>39.34</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="AE98">
-        <v>19.67</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="AF98">
         <v>76.31</v>
@@ -12792,7 +12822,7 @@
         <v>44.59</v>
       </c>
       <c r="AN98">
-        <v>35.36174070833012</v>
+        <v>35.361740708330117</v>
       </c>
     </row>
     <row r="99" spans="1:40">
@@ -12800,7 +12830,7 @@
         <v>137</v>
       </c>
       <c r="B99">
-        <v>94.13449939686369</v>
+        <v>94.134499396863689</v>
       </c>
       <c r="C99">
         <v>1657</v>
@@ -12812,22 +12842,22 @@
         <v>3.67</v>
       </c>
       <c r="F99">
-        <v>0.06832018887927971</v>
+        <v>6.8320188879279709E-2</v>
       </c>
       <c r="G99">
         <v>7.63</v>
       </c>
       <c r="H99">
-        <v>1.25153846290787</v>
+        <v>1.2515384629078701</v>
       </c>
       <c r="I99">
-        <v>29.55200004577637</v>
+        <v>29.552000045776371</v>
       </c>
       <c r="J99">
         <v>30.63024988174438</v>
       </c>
       <c r="K99">
-        <v>24.0104999923706</v>
+        <v>24.010499992370601</v>
       </c>
       <c r="L99">
         <v>19.13594994068146</v>
@@ -12866,7 +12896,7 @@
         <v>11.7</v>
       </c>
       <c r="Y99">
-        <v>34.13</v>
+        <v>34.130000000000003</v>
       </c>
       <c r="Z99">
         <v>3.13</v>
@@ -12881,7 +12911,7 @@
         <v>39.07</v>
       </c>
       <c r="AD99">
-        <v>-39.7</v>
+        <v>-39.700000000000003</v>
       </c>
       <c r="AE99">
         <v>9.68</v>
@@ -12911,7 +12941,7 @@
         <v>-7.91</v>
       </c>
       <c r="AN99">
-        <v>35.30041455315916</v>
+        <v>35.300414553159158</v>
       </c>
     </row>
     <row r="100" spans="1:40">
@@ -12931,31 +12961,31 @@
         <v>4.8</v>
       </c>
       <c r="F100">
-        <v>0.2806667218824466</v>
+        <v>0.28066672188244662</v>
       </c>
       <c r="G100">
         <v>4.55</v>
       </c>
       <c r="H100">
-        <v>0.3010165091759243</v>
+        <v>0.30101650917592432</v>
       </c>
       <c r="I100">
-        <v>4.108000040054321</v>
+        <v>4.1080000400543213</v>
       </c>
       <c r="J100">
-        <v>4.094500005245209</v>
+        <v>4.0945000052452087</v>
       </c>
       <c r="K100">
-        <v>3.529000010490417</v>
+        <v>3.5290000104904169</v>
       </c>
       <c r="L100">
-        <v>2.4613499969244</v>
+        <v>2.4613499969244002</v>
       </c>
       <c r="M100">
         <v>1</v>
       </c>
       <c r="N100">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -12988,10 +13018,10 @@
         <v>4.99</v>
       </c>
       <c r="Z100">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AA100">
-        <v>35.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="AB100">
         <v>34.21</v>
@@ -13030,7 +13060,7 @@
         <v>72.5</v>
       </c>
       <c r="AN100">
-        <v>35.2141597417253</v>
+        <v>35.214159741725297</v>
       </c>
     </row>
     <row r="101" spans="1:40">
@@ -13038,7 +13068,7 @@
         <v>139</v>
       </c>
       <c r="B101">
-        <v>99.71351025331725</v>
+        <v>99.713510253317253</v>
       </c>
       <c r="C101">
         <v>2440</v>
@@ -13056,19 +13086,19 @@
         <v>7.8</v>
       </c>
       <c r="H101">
-        <v>1.304002336977491</v>
+        <v>1.3040023369774909</v>
       </c>
       <c r="I101">
-        <v>18.95400009155274</v>
+        <v>18.954000091552739</v>
       </c>
       <c r="J101">
-        <v>15.88500018119812</v>
+        <v>15.885000181198119</v>
       </c>
       <c r="K101">
         <v>12.46900007247925</v>
       </c>
       <c r="L101">
-        <v>8.416900018453598</v>
+        <v>8.4169000184535978</v>
       </c>
       <c r="M101">
         <v>1.19</v>
@@ -13128,7 +13158,7 @@
         <v>23.92</v>
       </c>
       <c r="AG101">
-        <v>-36.63</v>
+        <v>-36.630000000000003</v>
       </c>
       <c r="AH101" t="s">
         <v>175</v>
@@ -13143,13 +13173,13 @@
         <v>-1.81</v>
       </c>
       <c r="AL101">
-        <v>-0.55</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="AM101">
         <v>69.61</v>
       </c>
       <c r="AN101">
-        <v>34.69629193819934</v>
+        <v>34.696291938199337</v>
       </c>
     </row>
     <row r="102" spans="1:40">
@@ -13157,7 +13187,7 @@
         <v>140</v>
       </c>
       <c r="B102">
-        <v>93.48612786489745</v>
+        <v>93.486127864897455</v>
       </c>
       <c r="C102">
         <v>3981</v>
@@ -13175,19 +13205,19 @@
         <v>2</v>
       </c>
       <c r="H102">
-        <v>-0.4859416018683818</v>
+        <v>-0.48594160186838181</v>
       </c>
       <c r="I102">
         <v>105.4039993286133</v>
       </c>
       <c r="J102">
-        <v>106.2189990997314</v>
+        <v>106.21899909973141</v>
       </c>
       <c r="K102">
         <v>103.8371997070312</v>
       </c>
       <c r="L102">
-        <v>91.91599979400635</v>
+        <v>91.915999794006353</v>
       </c>
       <c r="M102">
         <v>0.99</v>
@@ -13268,7 +13298,7 @@
         <v>38.39</v>
       </c>
       <c r="AN102">
-        <v>34.22058108779638</v>
+        <v>34.220581087796383</v>
       </c>
     </row>
     <row r="103" spans="1:40">
@@ -13276,7 +13306,7 @@
         <v>141</v>
       </c>
       <c r="B103">
-        <v>97.48190591073582</v>
+        <v>97.481905910735819</v>
       </c>
       <c r="C103">
         <v>1684</v>
@@ -13288,22 +13318,22 @@
         <v>1.65</v>
       </c>
       <c r="F103">
-        <v>-0.3112727285246115</v>
+        <v>-0.31127272852461152</v>
       </c>
       <c r="G103">
         <v>2.6</v>
       </c>
       <c r="H103">
-        <v>-0.3007749875050156</v>
+        <v>-0.30077498750501558</v>
       </c>
       <c r="I103">
         <v>55.46800079345703</v>
       </c>
       <c r="J103">
-        <v>53.70900020599365</v>
+        <v>53.709000205993647</v>
       </c>
       <c r="K103">
-        <v>50.05990020751953</v>
+        <v>50.059900207519533</v>
       </c>
       <c r="L103">
         <v>36.2008499622345</v>
@@ -13312,7 +13342,7 @@
         <v>1.03</v>
       </c>
       <c r="N103">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -13387,7 +13417,7 @@
         <v>42.4</v>
       </c>
       <c r="AN103">
-        <v>34.10612848110225</v>
+        <v>34.106128481102253</v>
       </c>
     </row>
     <row r="104" spans="1:40">
@@ -13395,7 +13425,7 @@
         <v>142</v>
       </c>
       <c r="B104">
-        <v>90.27442702050664</v>
+        <v>90.274427020506636</v>
       </c>
       <c r="C104">
         <v>2639</v>
@@ -13407,25 +13437,25 @@
         <v>1.89</v>
       </c>
       <c r="F104">
-        <v>-0.266172579922169</v>
+        <v>-0.26617257992216897</v>
       </c>
       <c r="G104">
         <v>2.4</v>
       </c>
       <c r="H104">
-        <v>-0.3624971922928044</v>
+        <v>-0.36249719229280442</v>
       </c>
       <c r="I104">
-        <v>94.06600189208984</v>
+        <v>94.066001892089844</v>
       </c>
       <c r="J104">
         <v>90.65800056457519</v>
       </c>
       <c r="K104">
-        <v>88.59820022583008</v>
+        <v>88.598200225830084</v>
       </c>
       <c r="L104">
-        <v>72.22195001602172</v>
+        <v>72.221950016021722</v>
       </c>
       <c r="M104">
         <v>1.04</v>
@@ -13470,7 +13500,7 @@
         <v>9.35</v>
       </c>
       <c r="AB104">
-        <v>17.56</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="AC104">
         <v>367.67</v>
@@ -13482,7 +13512,7 @@
         <v>-3.17</v>
       </c>
       <c r="AF104">
-        <v>32.63</v>
+        <v>32.630000000000003</v>
       </c>
       <c r="AG104">
         <v>-5</v>
@@ -13506,7 +13536,7 @@
         <v>52.31</v>
       </c>
       <c r="AN104">
-        <v>32.82862615662493</v>
+        <v>32.828626156624928</v>
       </c>
     </row>
     <row r="105" spans="1:40">
@@ -13526,19 +13556,19 @@
         <v>2</v>
       </c>
       <c r="F105">
-        <v>-0.2455016784793828</v>
+        <v>-0.24550167847938281</v>
       </c>
       <c r="G105">
         <v>2.61</v>
       </c>
       <c r="H105">
-        <v>-0.2976888772656263</v>
+        <v>-0.29768887726562632</v>
       </c>
       <c r="I105">
-        <v>156.3419982910156</v>
+        <v>156.34199829101561</v>
       </c>
       <c r="J105">
-        <v>158.4559997558594</v>
+        <v>158.45599975585941</v>
       </c>
       <c r="K105">
         <v>156.9194625854492</v>
@@ -13625,7 +13655,7 @@
         <v>31.92</v>
       </c>
       <c r="AN105">
-        <v>32.49189140456152</v>
+        <v>32.491891404561521</v>
       </c>
     </row>
     <row r="106" spans="1:40">
@@ -13633,7 +13663,7 @@
         <v>144</v>
       </c>
       <c r="B106">
-        <v>96.15500603136309</v>
+        <v>96.155006031363087</v>
       </c>
       <c r="C106">
         <v>3812.5</v>
@@ -13645,25 +13675,25 @@
         <v>3.05</v>
       </c>
       <c r="F106">
-        <v>-0.04818852834369683</v>
+        <v>-4.8188528343696829E-2</v>
       </c>
       <c r="G106">
         <v>3.84</v>
       </c>
       <c r="H106">
-        <v>0.08190268217927432</v>
+        <v>8.1902682179274322E-2</v>
       </c>
       <c r="I106">
-        <v>94.45999908447266</v>
+        <v>94.459999084472656</v>
       </c>
       <c r="J106">
-        <v>91.06599960327148</v>
+        <v>91.065999603271479</v>
       </c>
       <c r="K106">
-        <v>91.95609939575195</v>
+        <v>91.956099395751949</v>
       </c>
       <c r="L106">
-        <v>67.31862482070923</v>
+        <v>67.318624820709232</v>
       </c>
       <c r="M106">
         <v>1.04</v>
@@ -13702,7 +13732,7 @@
         <v>107</v>
       </c>
       <c r="Z106">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AA106" t="s">
         <v>155</v>
@@ -13735,7 +13765,7 @@
         <v>253</v>
       </c>
       <c r="AK106">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AL106">
         <v>3.09</v>
@@ -13744,7 +13774,7 @@
         <v>41.74</v>
       </c>
       <c r="AN106">
-        <v>32.38797781082813</v>
+        <v>32.387977810828133</v>
       </c>
     </row>
     <row r="107" spans="1:40">
@@ -13752,7 +13782,7 @@
         <v>145</v>
       </c>
       <c r="B107">
-        <v>90.39505428226779</v>
+        <v>90.395054282267793</v>
       </c>
       <c r="C107">
         <v>2729</v>
@@ -13764,19 +13794,19 @@
         <v>1.77</v>
       </c>
       <c r="F107">
-        <v>-0.2887226542233902</v>
+        <v>-0.28872265422339022</v>
       </c>
       <c r="G107">
         <v>2.76</v>
       </c>
       <c r="H107">
-        <v>-0.2513972236747848</v>
+        <v>-0.25139722367478479</v>
       </c>
       <c r="I107">
-        <v>24.87200012207031</v>
+        <v>24.872000122070311</v>
       </c>
       <c r="J107">
-        <v>25.19650001525879</v>
+        <v>25.196500015258788</v>
       </c>
       <c r="K107">
         <v>24.25339988708496</v>
@@ -13830,7 +13860,7 @@
         <v>19.55</v>
       </c>
       <c r="AC107">
-        <v>138.48</v>
+        <v>138.47999999999999</v>
       </c>
       <c r="AD107">
         <v>4.49</v>
@@ -13863,7 +13893,7 @@
         <v>198.48</v>
       </c>
       <c r="AN107">
-        <v>31.93570401796054</v>
+        <v>31.935704017960539</v>
       </c>
     </row>
     <row r="108" spans="1:40">
@@ -13871,37 +13901,37 @@
         <v>146</v>
       </c>
       <c r="B108">
-        <v>96.77322074788903</v>
+        <v>96.773220747889027</v>
       </c>
       <c r="C108">
         <v>2591</v>
       </c>
       <c r="D108">
-        <v>78.93000000000001</v>
+        <v>78.930000000000007</v>
       </c>
       <c r="E108">
         <v>2.23</v>
       </c>
       <c r="F108">
-        <v>-0.2022807027353754</v>
+        <v>-0.20228070273537541</v>
       </c>
       <c r="G108">
         <v>2.73</v>
       </c>
       <c r="H108">
-        <v>-0.260655554392953</v>
+        <v>-0.26065555439295301</v>
       </c>
       <c r="I108">
-        <v>78.70799865722657</v>
+        <v>78.707998657226568</v>
       </c>
       <c r="J108">
-        <v>79.19143867492676</v>
+        <v>79.191438674926758</v>
       </c>
       <c r="K108">
-        <v>78.20047439575195</v>
+        <v>78.200474395751954</v>
       </c>
       <c r="L108">
-        <v>58.72396070480347</v>
+        <v>58.723960704803467</v>
       </c>
       <c r="M108">
         <v>0.99</v>
@@ -13958,7 +13988,7 @@
         <v>18.48</v>
       </c>
       <c r="AF108">
-        <v>162.86</v>
+        <v>162.86000000000001</v>
       </c>
       <c r="AG108">
         <v>-51.39</v>
@@ -13982,7 +14012,7 @@
         <v>29.37</v>
       </c>
       <c r="AN108">
-        <v>29.55453620338172</v>
+        <v>29.554536203381719</v>
       </c>
     </row>
     <row r="109" spans="1:40">
@@ -13990,7 +14020,7 @@
         <v>147</v>
       </c>
       <c r="B109">
-        <v>93.86308805790109</v>
+        <v>93.863088057901095</v>
       </c>
       <c r="C109">
         <v>2291</v>
@@ -14002,22 +14032,22 @@
         <v>2.08</v>
       </c>
       <c r="F109">
-        <v>-0.230468295611902</v>
+        <v>-0.23046829561190199</v>
       </c>
       <c r="G109">
         <v>2.41</v>
       </c>
       <c r="H109">
-        <v>-0.3594110820534149</v>
+        <v>-0.35941108205341488</v>
       </c>
       <c r="I109">
-        <v>154.2099975585938</v>
+        <v>154.20999755859381</v>
       </c>
       <c r="J109">
-        <v>148.1335006713867</v>
+        <v>148.13350067138671</v>
       </c>
       <c r="K109">
-        <v>142.612600402832</v>
+        <v>142.61260040283199</v>
       </c>
       <c r="L109">
         <v>123.0284000396728</v>
@@ -14059,16 +14089,16 @@
         <v>159.12</v>
       </c>
       <c r="Z109">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AA109">
         <v>-49.95</v>
       </c>
       <c r="AB109">
-        <v>19.74</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="AC109">
-        <v>37.8</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AD109">
         <v>-26.1</v>
@@ -14095,7 +14125,7 @@
         <v>-2.93</v>
       </c>
       <c r="AL109">
-        <v>-1.1</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="AM109">
         <v>62.46</v>
@@ -14109,7 +14139,7 @@
         <v>148</v>
       </c>
       <c r="B110">
-        <v>95.50663449939685</v>
+        <v>95.506634499396853</v>
       </c>
       <c r="C110">
         <v>4987</v>
@@ -14121,7 +14151,7 @@
         <v>2.8</v>
       </c>
       <c r="F110">
-        <v>-0.09516784980457445</v>
+        <v>-9.5167849804574448E-2</v>
       </c>
       <c r="G110">
         <v>4.37</v>
@@ -14130,22 +14160,22 @@
         <v>0.2454665248669145</v>
       </c>
       <c r="I110">
-        <v>48.04599990844726</v>
+        <v>48.045999908447257</v>
       </c>
       <c r="J110">
-        <v>46.87650012969971</v>
+        <v>46.876500129699707</v>
       </c>
       <c r="K110">
-        <v>43.75860000610351</v>
+        <v>43.758600006103507</v>
       </c>
       <c r="L110">
-        <v>35.41832684516907</v>
+        <v>35.418326845169069</v>
       </c>
       <c r="M110">
         <v>1.02</v>
       </c>
       <c r="N110">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -14228,7 +14258,7 @@
         <v>149</v>
       </c>
       <c r="B111">
-        <v>90.78709288299156</v>
+        <v>90.787092882991558</v>
       </c>
       <c r="C111">
         <v>3210.5</v>
@@ -14237,34 +14267,34 @@
         <v>49.99</v>
       </c>
       <c r="E111">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F111">
-        <v>-0.408989717163237</v>
+        <v>-0.40898971716323701</v>
       </c>
       <c r="G111">
         <v>1.78</v>
       </c>
       <c r="H111">
-        <v>-0.5538360271349494</v>
+        <v>-0.55383602713494939</v>
       </c>
       <c r="I111">
-        <v>50.15200042724609</v>
+        <v>50.152000427246087</v>
       </c>
       <c r="J111">
-        <v>49.01449985504151</v>
+        <v>49.014499855041507</v>
       </c>
       <c r="K111">
-        <v>45.46340003967285</v>
+        <v>45.463400039672848</v>
       </c>
       <c r="L111">
-        <v>40.48755001068115</v>
+        <v>40.487550010681147</v>
       </c>
       <c r="M111">
         <v>1.02</v>
       </c>
       <c r="N111">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -14300,7 +14330,7 @@
         <v>1.98</v>
       </c>
       <c r="AA111">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AB111">
         <v>11.35</v>
@@ -14330,7 +14360,7 @@
         <v>240</v>
       </c>
       <c r="AK111">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AL111">
         <v>1.77</v>
@@ -14347,7 +14377,7 @@
         <v>150</v>
       </c>
       <c r="B112">
-        <v>94.33051869722557</v>
+        <v>94.330518697225571</v>
       </c>
       <c r="C112">
         <v>3340</v>
@@ -14365,19 +14395,19 @@
         <v>3</v>
       </c>
       <c r="H112">
-        <v>-0.1773305779294382</v>
+        <v>-0.17733057792943821</v>
       </c>
       <c r="I112">
         <v>30.77000007629395</v>
       </c>
       <c r="J112">
-        <v>30.50249996185303</v>
+        <v>30.502499961853029</v>
       </c>
       <c r="K112">
-        <v>28.92791286468506</v>
+        <v>28.927912864685059</v>
       </c>
       <c r="L112">
-        <v>21.31506443977356</v>
+        <v>21.315064439773561</v>
       </c>
       <c r="M112">
         <v>1.01</v>
@@ -14428,7 +14458,7 @@
         <v>174.05</v>
       </c>
       <c r="AD112">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AE112">
         <v>33.33</v>
@@ -14437,7 +14467,7 @@
         <v>12.5</v>
       </c>
       <c r="AG112">
-        <v>71.43000000000001</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="AH112" t="s">
         <v>155</v>
@@ -14458,7 +14488,7 @@
         <v>25</v>
       </c>
       <c r="AN112">
-        <v>26.01776153165699</v>
+        <v>26.017761531656991</v>
       </c>
     </row>
     <row r="113" spans="1:40">
@@ -14466,7 +14496,7 @@
         <v>151</v>
       </c>
       <c r="B113">
-        <v>90.01809408926418</v>
+        <v>90.018094089264181</v>
       </c>
       <c r="C113">
         <v>1714</v>
@@ -14478,31 +14508,31 @@
         <v>2.82</v>
       </c>
       <c r="F113">
-        <v>-0.09140950408770424</v>
+        <v>-9.1409504087704235E-2</v>
       </c>
       <c r="G113">
         <v>3</v>
       </c>
       <c r="H113">
-        <v>-0.1773305779294382</v>
+        <v>-0.17733057792943821</v>
       </c>
       <c r="I113">
-        <v>21.75800018310547</v>
+        <v>21.758000183105469</v>
       </c>
       <c r="J113">
-        <v>20.80299997329712</v>
+        <v>20.802999973297119</v>
       </c>
       <c r="K113">
-        <v>18.85220001220703</v>
+        <v>18.852200012207032</v>
       </c>
       <c r="L113">
-        <v>13.75749999046326</v>
+        <v>13.757499990463261</v>
       </c>
       <c r="M113">
         <v>1.05</v>
       </c>
       <c r="N113">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -14577,7 +14607,7 @@
         <v>1366.67</v>
       </c>
       <c r="AN113">
-        <v>25.66608996780896</v>
+        <v>25.666089967808961</v>
       </c>
     </row>
     <row r="114" spans="1:40">
@@ -14585,7 +14615,7 @@
         <v>152</v>
       </c>
       <c r="B114">
-        <v>95.26537997587454</v>
+        <v>95.265379975874538</v>
       </c>
       <c r="C114">
         <v>2069</v>
@@ -14597,31 +14627,31 @@
         <v>1.85</v>
       </c>
       <c r="F114">
-        <v>-0.2736892713559094</v>
+        <v>-0.27368927135590942</v>
       </c>
       <c r="G114">
         <v>3.45</v>
       </c>
       <c r="H114">
-        <v>-0.03845561715691358</v>
+        <v>-3.8455617156913577E-2</v>
       </c>
       <c r="I114">
-        <v>157.95</v>
+        <v>157.94999999999999</v>
       </c>
       <c r="J114">
         <v>151.2860008239746</v>
       </c>
       <c r="K114">
-        <v>142.8474005126953</v>
+        <v>142.84740051269529</v>
       </c>
       <c r="L114">
-        <v>132.4840001296997</v>
+        <v>132.48400012969969</v>
       </c>
       <c r="M114">
         <v>1.04</v>
       </c>
       <c r="N114">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -14648,13 +14678,13 @@
         <v>0</v>
       </c>
       <c r="X114">
-        <v>69.34999999999999</v>
+        <v>69.349999999999994</v>
       </c>
       <c r="Y114">
         <v>169.83</v>
       </c>
       <c r="Z114">
-        <v>4.89</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AA114">
         <v>28.81</v>
@@ -14696,7 +14726,7 @@
         <v>32.06</v>
       </c>
       <c r="AN114">
-        <v>23.44212811013344</v>
+        <v>23.442128110133439</v>
       </c>
     </row>
     <row r="115" spans="1:40">
@@ -14704,7 +14734,7 @@
         <v>153</v>
       </c>
       <c r="B115">
-        <v>94.63208685162847</v>
+        <v>94.632086851628472</v>
       </c>
       <c r="C115">
         <v>3503</v>
@@ -14716,25 +14746,25 @@
         <v>7.39</v>
       </c>
       <c r="F115">
-        <v>0.7673724922171387</v>
+        <v>0.76737249221713866</v>
       </c>
       <c r="G115">
         <v>4.47</v>
       </c>
       <c r="H115">
-        <v>0.2763276272608087</v>
+        <v>0.27632762726080867</v>
       </c>
       <c r="I115">
-        <v>32.96600036621093</v>
+        <v>32.966000366210928</v>
       </c>
       <c r="J115">
         <v>31.75950021743774</v>
       </c>
       <c r="K115">
-        <v>27.33220012664795</v>
+        <v>27.332200126647951</v>
       </c>
       <c r="L115">
-        <v>22.1018000125885</v>
+        <v>22.101800012588502</v>
       </c>
       <c r="M115">
         <v>1.04</v>
@@ -14794,7 +14824,7 @@
         <v>216.67</v>
       </c>
       <c r="AG115">
-        <v>-71.43000000000001</v>
+        <v>-71.430000000000007</v>
       </c>
       <c r="AH115" t="s">
         <v>177</v>
@@ -14823,13 +14853,13 @@
         <v>154</v>
       </c>
       <c r="B116">
-        <v>94.17973462002412</v>
+        <v>94.179734620024121</v>
       </c>
       <c r="C116">
         <v>3943</v>
       </c>
       <c r="D116">
-        <v>83.84999999999999</v>
+        <v>83.85</v>
       </c>
       <c r="E116">
         <v>2.42</v>
@@ -14841,25 +14871,25 @@
         <v>2.6</v>
       </c>
       <c r="H116">
-        <v>-0.3007749875050156</v>
+        <v>-0.30077498750501558</v>
       </c>
       <c r="I116">
-        <v>84.38199920654297</v>
+        <v>84.381999206542972</v>
       </c>
       <c r="J116">
-        <v>82.64500045776367</v>
+        <v>82.645000457763672</v>
       </c>
       <c r="K116">
-        <v>76.30010070800782</v>
+        <v>76.300100708007818</v>
       </c>
       <c r="L116">
-        <v>54.48645015716553</v>
+        <v>54.486450157165528</v>
       </c>
       <c r="M116">
         <v>1.02</v>
       </c>
       <c r="N116">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P116">
         <v>2</v>
@@ -14934,10 +14964,11 @@
         <v>86.58</v>
       </c>
       <c r="AN116">
-        <v>7.766654413740759</v>
+        <v>7.7666544137407589</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>